--- a/research/traditional_assets/database/data/south_africa/south_africa_investments_asset_management.xlsx
+++ b/research/traditional_assets/database/data/south_africa/south_africa_investments_asset_management.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ18"/>
+  <dimension ref="A1:AQ15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,124 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.1805</v>
+        <v>0.227</v>
       </c>
       <c r="E2">
-        <v>0.1378</v>
+        <v>0.08985</v>
       </c>
       <c r="F2">
-        <v>0.05769999999999999</v>
+        <v>-0.0277</v>
       </c>
       <c r="G2">
-        <v>0.2262256008235341</v>
+        <v>0.2828576927103215</v>
       </c>
       <c r="H2">
-        <v>0.2255861741299442</v>
+        <v>0.2827339757451303</v>
       </c>
       <c r="I2">
-        <v>0.2623058953953359</v>
+        <v>0.2631983267544811</v>
       </c>
       <c r="J2">
-        <v>0.2186308777686554</v>
+        <v>0.2312737334138957</v>
       </c>
       <c r="K2">
-        <v>698.77</v>
+        <v>372.156</v>
       </c>
       <c r="L2">
-        <v>0.2766638951577781</v>
+        <v>0.1967607303319104</v>
       </c>
       <c r="M2">
-        <v>437.904</v>
+        <v>380.63</v>
       </c>
       <c r="N2">
-        <v>0.05707969446544488</v>
+        <v>0.07733097119313137</v>
       </c>
       <c r="O2">
-        <v>0.6266783061665498</v>
+        <v>1.022770021173916</v>
       </c>
       <c r="P2">
-        <v>341.964</v>
+        <v>321.617</v>
       </c>
       <c r="Q2">
-        <v>0.04457415469642066</v>
+        <v>0.06534155206426538</v>
       </c>
       <c r="R2">
-        <v>0.4893799104140132</v>
+        <v>0.8641994217478692</v>
       </c>
       <c r="S2">
-        <v>95.93999999999998</v>
+        <v>59.01300000000001</v>
       </c>
       <c r="T2">
-        <v>0.2190891154225583</v>
+        <v>0.1550403278774663</v>
       </c>
       <c r="U2">
-        <v>1042.967</v>
+        <v>891.671</v>
       </c>
       <c r="V2">
-        <v>0.1359481477619333</v>
+        <v>0.1811569881899762</v>
       </c>
       <c r="W2">
-        <v>0.1814385446392173</v>
+        <v>0.106711915535445</v>
       </c>
       <c r="X2">
-        <v>0.06896257854376248</v>
+        <v>0.1047547349684686</v>
       </c>
       <c r="Y2">
-        <v>0.1124759660954548</v>
+        <v>0.001957180566976399</v>
       </c>
       <c r="Z2">
-        <v>1.262644188997193</v>
+        <v>0.7552270356020988</v>
       </c>
       <c r="AA2">
-        <v>0.1945989323921672</v>
+        <v>0.04328252009194256</v>
       </c>
       <c r="AB2">
-        <v>0.06582320530430327</v>
+        <v>0.1023167409492499</v>
       </c>
       <c r="AC2">
-        <v>0.1288485381567108</v>
+        <v>-0.06177038888978877</v>
       </c>
       <c r="AD2">
-        <v>1133.823</v>
+        <v>793.831</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>1133.823</v>
+        <v>793.831</v>
       </c>
       <c r="AG2">
-        <v>90.85599999999977</v>
+        <v>-97.84000000000003</v>
       </c>
       <c r="AH2">
-        <v>0.1287612472166932</v>
+        <v>0.138880680821166</v>
       </c>
       <c r="AI2">
-        <v>0.2586615528549264</v>
+        <v>0.2401232814598974</v>
       </c>
       <c r="AJ2">
-        <v>0.0117042414348903</v>
+        <v>-0.020280872674509</v>
       </c>
       <c r="AK2">
-        <v>0.02719868185660873</v>
+        <v>-0.04052587542352524</v>
       </c>
       <c r="AL2">
-        <v>62.34</v>
+        <v>45.192</v>
       </c>
       <c r="AM2">
-        <v>-1216.555</v>
+        <v>-405.172</v>
       </c>
       <c r="AN2">
-        <v>1.821332189602328</v>
+        <v>1.753493375508599</v>
       </c>
       <c r="AO2">
-        <v>10.62730189284568</v>
+        <v>11.01560010621349</v>
       </c>
       <c r="AP2">
-        <v>0.1459477867519963</v>
+        <v>-0.2161187858117929</v>
       </c>
       <c r="AQ2">
-        <v>-0.5445754610354648</v>
+        <v>-1.22865597820185</v>
       </c>
     </row>
     <row r="3">
@@ -716,7 +716,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>African Equity Empowerment Investments Limited (JSE:AEE)</t>
+          <t>Ninety One Group (LSE:N91)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -724,119 +724,119 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="D3">
-        <v>0.26</v>
+      <c r="F3">
+        <v>-0.0277</v>
       </c>
       <c r="G3">
-        <v>-0.1730192188468692</v>
+        <v>0.4524295630869742</v>
       </c>
       <c r="H3">
-        <v>-0.1735895846249225</v>
+        <v>0.4524295630869742</v>
       </c>
       <c r="I3">
-        <v>-0.2145071295722256</v>
+        <v>0.3615080985436233</v>
       </c>
       <c r="J3">
-        <v>-0.2145071295722256</v>
+        <v>0.2776361063714637</v>
       </c>
       <c r="K3">
-        <v>-9.18</v>
+        <v>210.2</v>
       </c>
       <c r="L3">
-        <v>-0.0569125852448853</v>
+        <v>0.2861031713624608</v>
       </c>
       <c r="M3">
-        <v>16.8</v>
+        <v>180.4</v>
       </c>
       <c r="N3">
-        <v>0.6412213740458016</v>
+        <v>0.08833178279390884</v>
       </c>
       <c r="O3">
-        <v>-1.830065359477124</v>
+        <v>0.8582302568981923</v>
       </c>
       <c r="P3">
-        <v>16.8</v>
+        <v>148.6</v>
       </c>
       <c r="Q3">
-        <v>0.6412213740458016</v>
+        <v>0.07276110267835284</v>
       </c>
       <c r="R3">
-        <v>-1.830065359477124</v>
+        <v>0.7069457659372027</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>31.80000000000001</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>0.1762749445676275</v>
       </c>
       <c r="U3">
-        <v>161.7</v>
+        <v>363.1</v>
       </c>
       <c r="V3">
-        <v>6.171755725190839</v>
+        <v>0.1777897468540371</v>
       </c>
       <c r="W3">
-        <v>-0.04870026525198939</v>
+        <v>0.5430121415654869</v>
       </c>
       <c r="X3">
-        <v>0.08618880217635545</v>
+        <v>0.1047547349684686</v>
       </c>
       <c r="Y3">
-        <v>-0.1348890674283448</v>
+        <v>0.4382574065970184</v>
       </c>
       <c r="Z3">
-        <v>-13.02907915993537</v>
+        <v>5.882305844675742</v>
       </c>
       <c r="AA3">
-        <v>2.794830371567042</v>
+        <v>1.633140491201877</v>
       </c>
       <c r="AB3">
-        <v>0.07098378943107898</v>
+        <v>0.1023167409492499</v>
       </c>
       <c r="AC3">
-        <v>2.723846582135963</v>
+        <v>1.530823750252627</v>
       </c>
       <c r="AD3">
-        <v>15.2</v>
+        <v>121.7</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>15.2</v>
+        <v>121.7</v>
       </c>
       <c r="AG3">
-        <v>-146.5</v>
+        <v>-241.4</v>
       </c>
       <c r="AH3">
-        <v>0.3671497584541063</v>
+        <v>0.05623844731977819</v>
       </c>
       <c r="AI3">
-        <v>0.0391147709727226</v>
+        <v>0.2438877755511022</v>
       </c>
       <c r="AJ3">
-        <v>1.217788861180382</v>
+        <v>-0.1340440890665779</v>
       </c>
       <c r="AK3">
-        <v>-0.6456588805641252</v>
+        <v>-1.776306107431936</v>
       </c>
       <c r="AL3">
-        <v>1.52</v>
+        <v>4.23</v>
       </c>
       <c r="AM3">
-        <v>-9.68</v>
+        <v>-3.35</v>
       </c>
       <c r="AN3">
-        <v>-0.5428571428571428</v>
+        <v>0.4485809067453004</v>
       </c>
       <c r="AO3">
-        <v>-22.76315789473684</v>
+        <v>62.78959810874704</v>
       </c>
       <c r="AP3">
-        <v>5.232142857142857</v>
+        <v>-0.8897899004791744</v>
       </c>
       <c r="AQ3">
-        <v>3.574380165289257</v>
+        <v>-79.28358208955225</v>
       </c>
     </row>
     <row r="4">
@@ -856,46 +856,46 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.0102</v>
+        <v>-0.0103</v>
       </c>
       <c r="E4">
-        <v>0.0164</v>
+        <v>-0.034</v>
       </c>
       <c r="G4">
-        <v>0.5140869565217392</v>
+        <v>0.5024177949709865</v>
       </c>
       <c r="H4">
-        <v>0.5140869565217392</v>
+        <v>0.5024177949709865</v>
       </c>
       <c r="I4">
-        <v>0.512</v>
+        <v>0.5</v>
       </c>
       <c r="J4">
-        <v>0.3793333333333334</v>
+        <v>0.3785942492012779</v>
       </c>
       <c r="K4">
-        <v>113.8</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="L4">
-        <v>0.3958260869565217</v>
+        <v>0.3438104448742746</v>
       </c>
       <c r="M4">
-        <v>104.7</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="N4">
-        <v>0.09092488059053409</v>
+        <v>0.1351052048726467</v>
       </c>
       <c r="O4">
-        <v>0.9200351493848858</v>
+        <v>1.20112517580872</v>
       </c>
       <c r="P4">
-        <v>104.7</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="Q4">
-        <v>0.09092488059053409</v>
+        <v>0.1351052048726467</v>
       </c>
       <c r="R4">
-        <v>0.9200351493848858</v>
+        <v>1.20112517580872</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -904,73 +904,73 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>40</v>
+        <v>36.4</v>
       </c>
       <c r="V4">
-        <v>0.03473729917498915</v>
+        <v>0.05758582502768549</v>
       </c>
       <c r="W4">
-        <v>0.8726993865030674</v>
+        <v>0.4708609271523179</v>
       </c>
       <c r="X4">
-        <v>0.06638152697386183</v>
+        <v>0.1043848982070629</v>
       </c>
       <c r="Y4">
-        <v>0.8063178595292056</v>
+        <v>0.3664760289452549</v>
       </c>
       <c r="Z4">
-        <v>4.190962099125364</v>
+        <v>2.764705882352941</v>
       </c>
       <c r="AA4">
-        <v>1.589771622934888</v>
+        <v>1.046701747791768</v>
       </c>
       <c r="AB4">
-        <v>0.0654290103783059</v>
+        <v>0.1022768997820443</v>
       </c>
       <c r="AC4">
-        <v>1.524342612556582</v>
+        <v>0.944424848009724</v>
       </c>
       <c r="AD4">
-        <v>36.3</v>
+        <v>32.6</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>36.3</v>
+        <v>32.6</v>
       </c>
       <c r="AG4">
-        <v>-3.700000000000003</v>
+        <v>-3.799999999999997</v>
       </c>
       <c r="AH4">
-        <v>0.03056070045462199</v>
+        <v>0.04904468181134346</v>
       </c>
       <c r="AI4">
-        <v>0.193806727175654</v>
+        <v>0.2235939643347051</v>
       </c>
       <c r="AJ4">
-        <v>-0.003223558111169196</v>
+        <v>-0.006048066210409035</v>
       </c>
       <c r="AK4">
-        <v>-0.02511880515953837</v>
+        <v>-0.03473491773308955</v>
       </c>
       <c r="AL4">
-        <v>2.6</v>
+        <v>3.33</v>
       </c>
       <c r="AM4">
-        <v>-195.2</v>
+        <v>-159.77</v>
       </c>
       <c r="AN4">
-        <v>0.2456021650879567</v>
+        <v>0.3137632338787296</v>
       </c>
       <c r="AO4">
-        <v>56.61538461538461</v>
+        <v>31.05105105105105</v>
       </c>
       <c r="AP4">
-        <v>-0.02503382949932343</v>
+        <v>-0.03657362848893164</v>
       </c>
       <c r="AQ4">
-        <v>-0.7540983606557375</v>
+        <v>-0.6471803217124618</v>
       </c>
     </row>
     <row r="5">
@@ -981,7 +981,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Ninety One Group (LSE:N91)</t>
+          <t>Sygnia Limited (JSE:SYG)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -989,119 +989,122 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="F5">
-        <v>0.05769999999999999</v>
+      <c r="D5">
+        <v>0.194</v>
+      </c>
+      <c r="E5">
+        <v>0.254</v>
       </c>
       <c r="G5">
-        <v>0.3215575620767494</v>
+        <v>0.4810690423162584</v>
       </c>
       <c r="H5">
-        <v>0.3215575620767494</v>
+        <v>0.4810690423162584</v>
       </c>
       <c r="I5">
-        <v>0.3446952595936794</v>
+        <v>0.4699331848552339</v>
       </c>
       <c r="J5">
-        <v>0.2617737856687194</v>
+        <v>0.3354859328652612</v>
       </c>
       <c r="K5">
-        <v>247.5</v>
+        <v>15.9</v>
       </c>
       <c r="L5">
-        <v>0.2793453724604966</v>
+        <v>0.3541202672605791</v>
       </c>
       <c r="M5">
-        <v>171.1</v>
+        <v>13.593</v>
       </c>
       <c r="N5">
-        <v>0.04999415614773258</v>
+        <v>0.08532956685499057</v>
       </c>
       <c r="O5">
-        <v>0.6913131313131313</v>
+        <v>0.8549056603773585</v>
       </c>
       <c r="P5">
-        <v>154.9</v>
+        <v>13.3</v>
       </c>
       <c r="Q5">
-        <v>0.04526063581112669</v>
+        <v>0.08349026993094789</v>
       </c>
       <c r="R5">
-        <v>0.6258585858585859</v>
+        <v>0.8364779874213837</v>
       </c>
       <c r="S5">
-        <v>16.19999999999999</v>
+        <v>0.2929999999999993</v>
       </c>
       <c r="T5">
-        <v>0.09468147282291052</v>
+        <v>0.02155521224159488</v>
       </c>
       <c r="U5">
-        <v>412.1</v>
+        <v>19.8</v>
       </c>
       <c r="V5">
-        <v>0.1204125759700795</v>
+        <v>0.1242937853107345</v>
       </c>
       <c r="W5">
-        <v>0.8817242607766299</v>
+        <v>0.3057692307692308</v>
       </c>
       <c r="X5">
-        <v>0.0668247150968843</v>
+        <v>0.1045628083187847</v>
       </c>
       <c r="Y5">
-        <v>0.8148995456797457</v>
+        <v>0.2012064224504461</v>
       </c>
       <c r="Z5">
-        <v>5.990534144692358</v>
+        <v>1.83115823817292</v>
       </c>
       <c r="AA5">
-        <v>1.568164801233842</v>
+        <v>0.6143278297573501</v>
       </c>
       <c r="AB5">
-        <v>0.06549825302661935</v>
+        <v>0.1022961409260572</v>
       </c>
       <c r="AC5">
-        <v>1.502666548207223</v>
+        <v>0.5120316888312929</v>
       </c>
       <c r="AD5">
-        <v>149.9</v>
+        <v>8.83</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>149.9</v>
+        <v>8.83</v>
       </c>
       <c r="AG5">
-        <v>-262.2</v>
+        <v>-10.97</v>
       </c>
       <c r="AH5">
-        <v>0.04196176133023542</v>
+        <v>0.0525188841967525</v>
       </c>
       <c r="AI5">
-        <v>0.2790914168683671</v>
+        <v>0.1590131460471817</v>
       </c>
       <c r="AJ5">
-        <v>-0.08296943231441049</v>
+        <v>-0.07395671812849727</v>
       </c>
       <c r="AK5">
-        <v>-2.097600000000001</v>
+        <v>-0.3070249090400224</v>
       </c>
       <c r="AL5">
-        <v>5.54</v>
+        <v>0.63</v>
       </c>
       <c r="AM5">
-        <v>-12.26</v>
+        <v>-256.37</v>
       </c>
       <c r="AN5">
-        <v>0.4786079182630907</v>
+        <v>0.4087962962962963</v>
       </c>
       <c r="AO5">
-        <v>55.12635379061371</v>
+        <v>33.49206349206349</v>
       </c>
       <c r="AP5">
-        <v>-0.8371647509578546</v>
+        <v>-0.5078703703703704</v>
       </c>
       <c r="AQ5">
-        <v>-24.91027732463295</v>
+        <v>-0.08230292155868471</v>
       </c>
     </row>
     <row r="6">
@@ -1121,121 +1124,121 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.00774</v>
+        <v>-0.0279</v>
       </c>
       <c r="E6">
-        <v>-0.263</v>
+        <v>-0.183</v>
       </c>
       <c r="G6">
-        <v>0.1868330341113106</v>
+        <v>0.2232415519399249</v>
       </c>
       <c r="H6">
-        <v>0.1856373429084381</v>
+        <v>0.2227784730913642</v>
       </c>
       <c r="I6">
-        <v>0.1608617594254937</v>
+        <v>0.1330830204422195</v>
       </c>
       <c r="J6">
-        <v>0.09935579258633435</v>
+        <v>0.09473968063944666</v>
       </c>
       <c r="K6">
-        <v>10.7</v>
+        <v>28.3</v>
       </c>
       <c r="L6">
-        <v>0.03842010771992818</v>
+        <v>0.1180642469753859</v>
       </c>
       <c r="M6">
-        <v>36</v>
+        <v>31.79</v>
       </c>
       <c r="N6">
-        <v>0.1041968162083936</v>
+        <v>0.08328530259365995</v>
       </c>
       <c r="O6">
-        <v>3.364485981308412</v>
+        <v>1.123321554770318</v>
       </c>
       <c r="P6">
-        <v>19.6</v>
+        <v>23.3</v>
       </c>
       <c r="Q6">
-        <v>0.05672937771345876</v>
+        <v>0.06104270369400053</v>
       </c>
       <c r="R6">
-        <v>1.83177570093458</v>
+        <v>0.823321554770318</v>
       </c>
       <c r="S6">
-        <v>16.4</v>
+        <v>8.489999999999998</v>
       </c>
       <c r="T6">
-        <v>0.4555555555555555</v>
+        <v>0.2670651148159798</v>
       </c>
       <c r="U6">
-        <v>158.2</v>
+        <v>149.2</v>
       </c>
       <c r="V6">
-        <v>0.4578871201157742</v>
+        <v>0.3908828923238145</v>
       </c>
       <c r="W6">
-        <v>0.04158569762922658</v>
+        <v>0.106711915535445</v>
       </c>
       <c r="X6">
-        <v>0.0697471675425658</v>
+        <v>0.106236071980911</v>
       </c>
       <c r="Y6">
-        <v>-0.02816146991333922</v>
+        <v>0.0004758435545339085</v>
       </c>
       <c r="Z6">
-        <v>5.887949260042282</v>
+        <v>4.183246073298427</v>
       </c>
       <c r="AA6">
-        <v>0.5850018654396218</v>
+        <v>0.3963193970205123</v>
       </c>
       <c r="AB6">
-        <v>0.06591700574930695</v>
+        <v>0.1024704552939412</v>
       </c>
       <c r="AC6">
-        <v>0.5190848596903149</v>
+        <v>0.2938489417265711</v>
       </c>
       <c r="AD6">
-        <v>43.1</v>
+        <v>35</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>43.1</v>
+        <v>35</v>
       </c>
       <c r="AG6">
-        <v>-115.1</v>
+        <v>-114.2</v>
       </c>
       <c r="AH6">
-        <v>0.1109109624292331</v>
+        <v>0.083993280537557</v>
       </c>
       <c r="AI6">
-        <v>0.1387636831938184</v>
+        <v>0.1332825590251333</v>
       </c>
       <c r="AJ6">
-        <v>-0.4995659722222222</v>
+        <v>-0.4269158878504672</v>
       </c>
       <c r="AK6">
-        <v>-0.7552493438320209</v>
+        <v>-1.00705467372134</v>
       </c>
       <c r="AL6">
-        <v>4.27</v>
+        <v>3.27</v>
       </c>
       <c r="AM6">
-        <v>-3.66</v>
+        <v>-3.33</v>
       </c>
       <c r="AN6">
-        <v>0.8304431599229287</v>
+        <v>0.925925925925926</v>
       </c>
       <c r="AO6">
-        <v>10.49180327868853</v>
+        <v>9.755351681957187</v>
       </c>
       <c r="AP6">
-        <v>-2.217726396917148</v>
+        <v>-3.021164021164021</v>
       </c>
       <c r="AQ6">
-        <v>-12.24043715846994</v>
+        <v>-9.57957957957958</v>
       </c>
     </row>
     <row r="7">
@@ -1246,7 +1249,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Sygnia Limited (JSE:SYG)</t>
+          <t>Sabvest Capital Limited (JSE:SBP)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1255,121 +1258,121 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.224</v>
+        <v>0.507</v>
       </c>
       <c r="E7">
-        <v>0.277</v>
+        <v>1.769</v>
       </c>
       <c r="G7">
-        <v>0.3655462184873949</v>
+        <v>0.8858195211786373</v>
       </c>
       <c r="H7">
-        <v>0.3655462184873949</v>
+        <v>0.8858195211786373</v>
       </c>
       <c r="I7">
-        <v>0.430672268907563</v>
+        <v>0.8839779005524863</v>
       </c>
       <c r="J7">
-        <v>0.3012683946818164</v>
+        <v>0.8067721053754773</v>
       </c>
       <c r="K7">
-        <v>14.9</v>
+        <v>42.6</v>
       </c>
       <c r="L7">
-        <v>0.3130252100840336</v>
+        <v>0.7845303867403316</v>
       </c>
       <c r="M7">
-        <v>10.8</v>
+        <v>5.008</v>
       </c>
       <c r="N7">
-        <v>0.06390532544378699</v>
+        <v>0.02562947799385875</v>
       </c>
       <c r="O7">
-        <v>0.7248322147651007</v>
+        <v>0.1175586854460094</v>
       </c>
       <c r="P7">
-        <v>10.8</v>
+        <v>0.878</v>
       </c>
       <c r="Q7">
-        <v>0.06390532544378699</v>
+        <v>0.004493346980552712</v>
       </c>
       <c r="R7">
-        <v>0.7248322147651007</v>
+        <v>0.02061032863849765</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>4.13</v>
       </c>
       <c r="T7">
-        <v>0</v>
+        <v>0.8246805111821086</v>
       </c>
       <c r="U7">
-        <v>32.3</v>
+        <v>9.17</v>
       </c>
       <c r="V7">
-        <v>0.1911242603550296</v>
+        <v>0.04692937563971341</v>
       </c>
       <c r="W7">
-        <v>0.4127423822714681</v>
+        <v>0.2047092743873138</v>
       </c>
       <c r="X7">
-        <v>0.06838374647955944</v>
+        <v>0.1059722643170933</v>
       </c>
       <c r="Y7">
-        <v>0.3443586357919087</v>
+        <v>0.09873701007022054</v>
       </c>
       <c r="Z7">
-        <v>1.511111111111111</v>
+        <v>0.2330102086793084</v>
       </c>
       <c r="AA7">
-        <v>0.4552500186303003</v>
+        <v>0.187986136630185</v>
       </c>
       <c r="AB7">
-        <v>0.06572940485929959</v>
+        <v>0.102443745850982</v>
       </c>
       <c r="AC7">
-        <v>0.3895206137710008</v>
+        <v>0.085542390779203</v>
       </c>
       <c r="AD7">
-        <v>14.7</v>
+        <v>16.8</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>14.7</v>
+        <v>16.8</v>
       </c>
       <c r="AG7">
-        <v>-17.6</v>
+        <v>7.630000000000001</v>
       </c>
       <c r="AH7">
-        <v>0.08002177463255308</v>
+        <v>0.07917059377945335</v>
       </c>
       <c r="AI7">
-        <v>0.2318611987381703</v>
+        <v>0.06749698674166332</v>
       </c>
       <c r="AJ7">
-        <v>-0.1162483487450462</v>
+        <v>0.0375806531054524</v>
       </c>
       <c r="AK7">
-        <v>-0.5659163987138262</v>
+        <v>0.03182747257331164</v>
       </c>
       <c r="AL7">
-        <v>0.996</v>
+        <v>1.25</v>
       </c>
       <c r="AM7">
-        <v>-1025.304</v>
+        <v>1.25</v>
       </c>
       <c r="AN7">
-        <v>0.6933962264150944</v>
+        <v>0.3492723492723493</v>
       </c>
       <c r="AO7">
-        <v>20.58232931726907</v>
+        <v>38.4</v>
       </c>
       <c r="AP7">
-        <v>-0.8301886792452829</v>
+        <v>0.1586278586278586</v>
       </c>
       <c r="AQ7">
-        <v>-0.0199940700514189</v>
+        <v>38.4</v>
       </c>
     </row>
     <row r="8">
@@ -1380,7 +1383,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Sabvest Capital Limited (JSE:SBP)</t>
+          <t>YeboYethu (RF) Limited (JSE:YYLBEE)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1389,121 +1392,112 @@
         </is>
       </c>
       <c r="D8">
-        <v>0.253</v>
-      </c>
-      <c r="E8">
-        <v>0.335</v>
+        <v>1.16</v>
       </c>
       <c r="G8">
-        <v>0.4062947067238912</v>
+        <v>0</v>
       </c>
       <c r="H8">
-        <v>0.4062947067238912</v>
+        <v>0</v>
       </c>
       <c r="I8">
-        <v>0.9227467811158797</v>
+        <v>0.9833333333333334</v>
       </c>
       <c r="J8">
-        <v>0.7852025508899861</v>
+        <v>0.9833333333333334</v>
       </c>
       <c r="K8">
-        <v>54.3</v>
+        <v>-79.5</v>
       </c>
       <c r="L8">
-        <v>0.7768240343347639</v>
+        <v>-1.472222222222222</v>
       </c>
       <c r="M8">
-        <v>4.162</v>
+        <v>6.47</v>
       </c>
       <c r="N8">
-        <v>0.02752645502645503</v>
+        <v>0.05587219343696027</v>
       </c>
       <c r="O8">
-        <v>0.07664825046040516</v>
+        <v>-0.08138364779874213</v>
       </c>
       <c r="P8">
-        <v>0.712</v>
+        <v>6.47</v>
       </c>
       <c r="Q8">
-        <v>0.004708994708994709</v>
+        <v>0.05587219343696027</v>
       </c>
       <c r="R8">
-        <v>0.01311233885819521</v>
+        <v>-0.08138364779874213</v>
       </c>
       <c r="S8">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="T8">
-        <v>0.8289283998077848</v>
+        <v>0</v>
       </c>
       <c r="U8">
-        <v>5.91</v>
+        <v>0.311</v>
       </c>
       <c r="V8">
-        <v>0.03908730158730159</v>
+        <v>0.00268566493955095</v>
       </c>
       <c r="W8">
-        <v>0.3425867507886435</v>
+        <v>-0.2207107162687396</v>
       </c>
       <c r="X8">
-        <v>0.06954141060796551</v>
+        <v>0.2977211229349253</v>
       </c>
       <c r="Y8">
-        <v>0.2730453401806781</v>
+        <v>-0.5184318392036649</v>
       </c>
       <c r="Z8">
-        <v>0.4010327022375215</v>
+        <v>0.05548551365714269</v>
       </c>
       <c r="AA8">
-        <v>0.3148919007872061</v>
+        <v>0.05456075509619032</v>
       </c>
       <c r="AB8">
-        <v>0.06647657727191081</v>
+        <v>0.1064870035202336</v>
       </c>
       <c r="AC8">
-        <v>0.2484153235152953</v>
+        <v>-0.05192624842404327</v>
       </c>
       <c r="AD8">
-        <v>18</v>
+        <v>491.2</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>18</v>
+        <v>491.2</v>
       </c>
       <c r="AG8">
-        <v>12.09</v>
+        <v>490.889</v>
       </c>
       <c r="AH8">
-        <v>0.1063829787234043</v>
+        <v>0.8092257001647446</v>
       </c>
       <c r="AI8">
-        <v>0.07199999999999999</v>
+        <v>0.6965399886557004</v>
       </c>
       <c r="AJ8">
-        <v>0.07404005144221937</v>
+        <v>0.809127905730943</v>
       </c>
       <c r="AK8">
-        <v>0.0495309107296489</v>
+        <v>0.6964061008187105</v>
       </c>
       <c r="AL8">
-        <v>1.62</v>
+        <v>27</v>
       </c>
       <c r="AM8">
-        <v>1.62</v>
-      </c>
-      <c r="AN8">
-        <v>0.2790697674418605</v>
+        <v>26.971</v>
       </c>
       <c r="AO8">
-        <v>39.81481481481481</v>
-      </c>
-      <c r="AP8">
-        <v>0.1874418604651163</v>
+        <v>1.966666666666667</v>
       </c>
       <c r="AQ8">
-        <v>39.81481481481481</v>
+        <v>1.968781283600905</v>
       </c>
     </row>
     <row r="9">
@@ -1514,7 +1508,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>NVest Financial Holdings Limited (JSE:NVE)</t>
+          <t>MTN Zakhele Futhi (RF) Limited (JSE:MTNZF)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1522,122 +1516,107 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="D9">
-        <v>0.00758</v>
-      </c>
-      <c r="E9">
-        <v>-0.00371</v>
-      </c>
       <c r="G9">
-        <v>0.2702020202020202</v>
+        <v>0</v>
       </c>
       <c r="H9">
-        <v>0.2702020202020202</v>
+        <v>0</v>
       </c>
       <c r="I9">
-        <v>0.2909090909090909</v>
+        <v>0.9361702127659575</v>
       </c>
       <c r="J9">
-        <v>0.2119547657512116</v>
+        <v>0.9361702127659575</v>
       </c>
       <c r="K9">
-        <v>4.46</v>
+        <v>27.3</v>
       </c>
       <c r="L9">
-        <v>0.2252525252525252</v>
+        <v>1.936170212765957</v>
       </c>
       <c r="M9">
-        <v>10.74</v>
+        <v>-0</v>
       </c>
       <c r="N9">
-        <v>0.3274390243902439</v>
+        <v>-0</v>
       </c>
       <c r="O9">
-        <v>2.408071748878924</v>
+        <v>-0</v>
       </c>
       <c r="P9">
-        <v>2.4</v>
+        <v>-0</v>
       </c>
       <c r="Q9">
-        <v>0.07317073170731708</v>
+        <v>-0</v>
       </c>
       <c r="R9">
-        <v>0.5381165919282511</v>
+        <v>-0</v>
       </c>
       <c r="S9">
-        <v>8.34</v>
-      </c>
-      <c r="T9">
-        <v>0.776536312849162</v>
+        <v>0</v>
       </c>
       <c r="U9">
-        <v>4.81</v>
+        <v>1.79</v>
       </c>
       <c r="V9">
-        <v>0.1466463414634146</v>
+        <v>0.01271306818181818</v>
       </c>
       <c r="W9">
-        <v>0.1537931034482758</v>
+        <v>0.1153358681875792</v>
       </c>
       <c r="X9">
-        <v>0.07271721779866189</v>
+        <v>0.1193404901613316</v>
       </c>
       <c r="Y9">
-        <v>0.08107588564961396</v>
+        <v>-0.00400462197375237</v>
       </c>
       <c r="Z9">
-        <v>1.001517450682853</v>
+        <v>0.04623360100730228</v>
       </c>
       <c r="AA9">
-        <v>0.2122763966552347</v>
+        <v>0.04328252009194256</v>
       </c>
       <c r="AB9">
-        <v>0.06723149455208813</v>
+        <v>0.1050529089817313</v>
       </c>
       <c r="AC9">
-        <v>0.1450449021031466</v>
+        <v>-0.06177038888978877</v>
       </c>
       <c r="AD9">
-        <v>6.79</v>
+        <v>52.9</v>
       </c>
       <c r="AE9">
         <v>0</v>
       </c>
       <c r="AF9">
-        <v>6.79</v>
+        <v>52.9</v>
       </c>
       <c r="AG9">
-        <v>1.98</v>
+        <v>51.11</v>
       </c>
       <c r="AH9">
-        <v>0.1715079565546855</v>
+        <v>0.2731027361899845</v>
       </c>
       <c r="AI9">
-        <v>0.1997646366578405</v>
+        <v>0.1524495677233429</v>
       </c>
       <c r="AJ9">
-        <v>0.05692926969522715</v>
+        <v>0.2663227554582877</v>
       </c>
       <c r="AK9">
-        <v>0.06785469499657301</v>
+        <v>0.1480548072187943</v>
       </c>
       <c r="AL9">
-        <v>0.517</v>
+        <v>3.89</v>
       </c>
       <c r="AM9">
-        <v>0.02900000000000003</v>
-      </c>
-      <c r="AN9">
-        <v>1.145025295109612</v>
+        <v>3.842</v>
       </c>
       <c r="AO9">
-        <v>11.14119922630561</v>
-      </c>
-      <c r="AP9">
-        <v>0.3338954468802699</v>
+        <v>3.39331619537275</v>
       </c>
       <c r="AQ9">
-        <v>198.6206896551722</v>
+        <v>3.435710567412805</v>
       </c>
     </row>
     <row r="10">
@@ -1648,7 +1627,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>RH Bophelo Limited (JSE:RHB)</t>
+          <t>PSG Konsult Limited (JSE:KST)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1656,110 +1635,110 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="D10">
+        <v>0.106</v>
+      </c>
+      <c r="E10">
+        <v>0.126</v>
+      </c>
       <c r="G10">
-        <v>0.9016393442622951</v>
+        <v>0</v>
       </c>
       <c r="H10">
-        <v>0.9016393442622951</v>
+        <v>0</v>
       </c>
       <c r="I10">
-        <v>0.8770491803278688</v>
+        <v>0</v>
       </c>
       <c r="J10">
-        <v>0.6926229508196721</v>
+        <v>0</v>
       </c>
       <c r="K10">
-        <v>8.43</v>
+        <v>54.3</v>
       </c>
       <c r="L10">
-        <v>0.6909836065573771</v>
+        <v>0.1486042692939245</v>
       </c>
       <c r="M10">
-        <v>0.669</v>
+        <v>39</v>
       </c>
       <c r="N10">
-        <v>0.03263414634146342</v>
+        <v>0.04240513210829618</v>
       </c>
       <c r="O10">
-        <v>0.07935943060498221</v>
+        <v>0.7182320441988951</v>
       </c>
       <c r="P10">
-        <v>0.669</v>
+        <v>24.7</v>
       </c>
       <c r="Q10">
-        <v>0.03263414634146342</v>
+        <v>0.02685658366858758</v>
       </c>
       <c r="R10">
-        <v>0.07935943060498221</v>
+        <v>0.4548802946593002</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="T10">
-        <v>0</v>
+        <v>0.3666666666666667</v>
       </c>
       <c r="U10">
-        <v>1.06</v>
+        <v>114.8</v>
       </c>
       <c r="V10">
-        <v>0.05170731707317074</v>
+        <v>0.1248233119495488</v>
       </c>
       <c r="W10">
-        <v>0.1890134529147982</v>
+        <v>0.2102206736353077</v>
       </c>
       <c r="X10">
-        <v>0.06565022650917374</v>
+        <v>0.1027728521473979</v>
       </c>
       <c r="Y10">
-        <v>0.1233632264056244</v>
+        <v>0.1074478214879099</v>
       </c>
       <c r="Z10">
-        <v>0.2904761904761904</v>
+        <v>2.244471744471744</v>
       </c>
       <c r="AA10">
-        <v>0.2011904761904762</v>
+        <v>0</v>
       </c>
       <c r="AB10">
-        <v>0.06537256910822403</v>
+        <v>0.1020959026401986</v>
       </c>
       <c r="AC10">
-        <v>0.1358179070822521</v>
+        <v>-0.1020959026401986</v>
       </c>
       <c r="AD10">
-        <v>0.231</v>
+        <v>15.3</v>
       </c>
       <c r="AE10">
         <v>0</v>
       </c>
       <c r="AF10">
-        <v>0.231</v>
+        <v>15.3</v>
       </c>
       <c r="AG10">
-        <v>-0.8290000000000001</v>
+        <v>-99.5</v>
       </c>
       <c r="AH10">
-        <v>0.01114273310501182</v>
+        <v>0.01636363636363636</v>
       </c>
       <c r="AI10">
-        <v>0.003602002151845442</v>
+        <v>0.05385427666314678</v>
       </c>
       <c r="AJ10">
-        <v>-0.04214325657058614</v>
+        <v>-0.1213118751524018</v>
       </c>
       <c r="AK10">
-        <v>-0.01314391717271012</v>
+        <v>-0.5877141169521559</v>
       </c>
       <c r="AL10">
-        <v>0.008</v>
+        <v>0</v>
       </c>
       <c r="AM10">
-        <v>0.008</v>
-      </c>
-      <c r="AO10">
-        <v>1337.5</v>
-      </c>
-      <c r="AQ10">
-        <v>1337.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1770,7 +1749,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Long4life Limited (JSE:L4L)</t>
+          <t>Purple Group Limited (JSE:PPE)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1778,116 +1757,107 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="D11">
+        <v>0.312</v>
+      </c>
       <c r="G11">
-        <v>0.09768451519536904</v>
+        <v>0.001949685534591195</v>
       </c>
       <c r="H11">
-        <v>0.09768451519536904</v>
+        <v>0</v>
       </c>
       <c r="I11">
-        <v>0.119753979739508</v>
+        <v>0</v>
       </c>
       <c r="J11">
-        <v>0.08713367032877441</v>
+        <v>0</v>
       </c>
       <c r="K11">
-        <v>25.7</v>
+        <v>2.58</v>
       </c>
       <c r="L11">
-        <v>0.09298118668596238</v>
+        <v>0.1622641509433962</v>
       </c>
       <c r="M11">
-        <v>26.573</v>
+        <v>-0</v>
       </c>
       <c r="N11">
-        <v>0.1141451890034364</v>
+        <v>-0</v>
       </c>
       <c r="O11">
-        <v>1.033968871595331</v>
+        <v>-0</v>
       </c>
       <c r="P11">
-        <v>0.073</v>
+        <v>-0</v>
       </c>
       <c r="Q11">
-        <v>0.000313573883161512</v>
+        <v>-0</v>
       </c>
       <c r="R11">
-        <v>0.002840466926070039</v>
+        <v>-0</v>
       </c>
       <c r="S11">
-        <v>26.5</v>
-      </c>
-      <c r="T11">
-        <v>0.9972528506378655</v>
+        <v>0</v>
       </c>
       <c r="U11">
-        <v>46</v>
+        <v>5.55</v>
       </c>
       <c r="V11">
-        <v>0.1975945017182131</v>
+        <v>0.04356357927786499</v>
       </c>
       <c r="W11">
-        <v>0.09476401179941003</v>
+        <v>0.09626865671641791</v>
       </c>
       <c r="X11">
-        <v>0.07140018747313438</v>
+        <v>0.1024217660847348</v>
       </c>
       <c r="Y11">
-        <v>0.02336382432627565</v>
+        <v>-0.006153109368316867</v>
       </c>
       <c r="Z11">
-        <v>2.157689305230289</v>
+        <v>3.111545988258317</v>
       </c>
       <c r="AA11">
-        <v>0.1880073885938583</v>
+        <v>0</v>
       </c>
       <c r="AB11">
-        <v>0.06612821936268884</v>
+        <v>0.1021051063565227</v>
       </c>
       <c r="AC11">
-        <v>0.1218791692311694</v>
+        <v>-0.1021051063565227</v>
       </c>
       <c r="AD11">
-        <v>39.7</v>
+        <v>1.15</v>
       </c>
       <c r="AE11">
         <v>0</v>
       </c>
       <c r="AF11">
-        <v>39.7</v>
+        <v>1.15</v>
       </c>
       <c r="AG11">
-        <v>-6.299999999999997</v>
+        <v>-4.4</v>
       </c>
       <c r="AH11">
-        <v>0.1456880733944954</v>
+        <v>0.00894593543368339</v>
       </c>
       <c r="AI11">
-        <v>0.1103390772651473</v>
+        <v>0.03427719821162444</v>
       </c>
       <c r="AJ11">
-        <v>-0.02781456953642383</v>
+        <v>-0.03577235772357724</v>
       </c>
       <c r="AK11">
-        <v>-0.02007648183556405</v>
+        <v>-0.1571428571428572</v>
       </c>
       <c r="AL11">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="AM11">
-        <v>1.14</v>
-      </c>
-      <c r="AN11">
-        <v>0.9974874371859298</v>
-      </c>
-      <c r="AO11">
-        <v>9.76401179941003</v>
-      </c>
-      <c r="AP11">
-        <v>-0.1582914572864321</v>
+        <v>-0.427</v>
       </c>
       <c r="AQ11">
-        <v>29.03508771929824</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="12">
@@ -1898,7 +1868,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>YeboYethu (RF) Limited (JSE:YYLBEE)</t>
+          <t>Zeder Investments Ltd. (JSE:ZED)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1906,116 +1876,89 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="D12">
-        <v>1.188</v>
-      </c>
-      <c r="E12">
-        <v>0.555</v>
-      </c>
-      <c r="G12">
-        <v>0</v>
-      </c>
-      <c r="H12">
-        <v>0</v>
-      </c>
-      <c r="I12">
-        <v>0.9811320754716981</v>
-      </c>
-      <c r="J12">
-        <v>0.8264187903091678</v>
-      </c>
       <c r="K12">
-        <v>86</v>
-      </c>
-      <c r="L12">
-        <v>1.352201257861635</v>
+        <v>6.51</v>
       </c>
       <c r="M12">
-        <v>7.01</v>
+        <v>-0</v>
       </c>
       <c r="N12">
-        <v>0.04145476049674748</v>
+        <v>-0</v>
       </c>
       <c r="O12">
-        <v>0.08151162790697675</v>
+        <v>-0</v>
       </c>
       <c r="P12">
-        <v>7.01</v>
+        <v>-0</v>
       </c>
       <c r="Q12">
-        <v>0.04145476049674748</v>
+        <v>-0</v>
       </c>
       <c r="R12">
-        <v>0.08151162790697675</v>
+        <v>-0</v>
       </c>
       <c r="S12">
         <v>0</v>
       </c>
-      <c r="T12">
-        <v>0</v>
-      </c>
       <c r="U12">
-        <v>0.391</v>
+        <v>25.9</v>
       </c>
       <c r="V12">
-        <v>0.00231224127735068</v>
+        <v>0.1665594855305466</v>
       </c>
       <c r="W12">
-        <v>0.6164874551971327</v>
+        <v>0.01379237288135593</v>
       </c>
       <c r="X12">
-        <v>0.2009882131516332</v>
+        <v>0.1020052760592112</v>
       </c>
       <c r="Y12">
-        <v>0.4154992420454995</v>
+        <v>-0.08821290317785524</v>
       </c>
       <c r="Z12">
-        <v>0.09251043651544022</v>
+        <v>0</v>
       </c>
       <c r="AA12">
-        <v>0.07645236303606318</v>
+        <v>-0.004280510018214936</v>
       </c>
       <c r="AB12">
-        <v>0.07004081633506409</v>
+        <v>0.1020052760592112</v>
       </c>
       <c r="AC12">
-        <v>0.006411546700999082</v>
+        <v>-0.1062857860774261</v>
       </c>
       <c r="AD12">
-        <v>635.8</v>
+        <v>0</v>
       </c>
       <c r="AE12">
         <v>0</v>
       </c>
       <c r="AF12">
-        <v>635.8</v>
+        <v>0</v>
       </c>
       <c r="AG12">
-        <v>635.409</v>
+        <v>-25.9</v>
       </c>
       <c r="AH12">
-        <v>0.7899117902845073</v>
+        <v>0</v>
       </c>
       <c r="AI12">
-        <v>0.7204532577903682</v>
+        <v>0</v>
       </c>
       <c r="AJ12">
-        <v>0.7898096851620057</v>
+        <v>-0.1998456790123457</v>
       </c>
       <c r="AK12">
-        <v>0.7203293470534821</v>
+        <v>-0.1192998618148319</v>
       </c>
       <c r="AL12">
-        <v>32.1</v>
+        <v>0</v>
       </c>
       <c r="AM12">
-        <v>32.057</v>
-      </c>
-      <c r="AO12">
-        <v>1.94392523364486</v>
+        <v>-2.29</v>
       </c>
       <c r="AQ12">
-        <v>1.946532738559441</v>
+        <v>0.8209606986899562</v>
       </c>
     </row>
     <row r="13">
@@ -2026,7 +1969,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Trematon Capital Investments Limited (JSE:TMT)</t>
+          <t>Mahube Infrastructure Limited (JSE:MHB)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2034,119 +1977,104 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="D13">
-        <v>0.249</v>
-      </c>
-      <c r="G13">
-        <v>0.2535971223021583</v>
-      </c>
-      <c r="H13">
-        <v>0.2535971223021583</v>
-      </c>
-      <c r="I13">
-        <v>0.226978417266187</v>
-      </c>
-      <c r="J13">
-        <v>0.226978417266187</v>
+      <c r="E13">
+        <v>0.0537</v>
       </c>
       <c r="K13">
-        <v>-1.14</v>
-      </c>
-      <c r="L13">
-        <v>-0.04100719424460431</v>
+        <v>2.83</v>
       </c>
       <c r="M13">
-        <v>1.15</v>
+        <v>1.94</v>
       </c>
       <c r="N13">
-        <v>0.02346938775510204</v>
+        <v>0.1026455026455027</v>
       </c>
       <c r="O13">
-        <v>-1.008771929824561</v>
+        <v>0.6855123674911661</v>
       </c>
       <c r="P13">
-        <v>-0</v>
+        <v>1.94</v>
       </c>
       <c r="Q13">
-        <v>-0</v>
+        <v>0.1026455026455027</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>0.6855123674911661</v>
       </c>
       <c r="S13">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="T13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U13">
-        <v>14</v>
+        <v>1.47</v>
       </c>
       <c r="V13">
-        <v>0.2857142857142857</v>
+        <v>0.07777777777777778</v>
       </c>
       <c r="W13">
-        <v>-0.02150943396226415</v>
+        <v>0.06819277108433736</v>
       </c>
       <c r="X13">
-        <v>0.125661090264748</v>
+        <v>0.1020321299410501</v>
       </c>
       <c r="Y13">
-        <v>-0.1471705242270122</v>
+        <v>-0.03383935885671271</v>
       </c>
       <c r="Z13">
-        <v>0.2485249418916503</v>
+        <v>0</v>
       </c>
       <c r="AA13">
-        <v>0.05640979796173788</v>
+        <v>-0.01931177598936593</v>
       </c>
       <c r="AB13">
-        <v>0.07112623722519967</v>
+        <v>0.1020117671068376</v>
       </c>
       <c r="AC13">
-        <v>-0.01471643926346179</v>
+        <v>-0.1213235430962036</v>
       </c>
       <c r="AD13">
-        <v>82</v>
+        <v>0.011</v>
       </c>
       <c r="AE13">
         <v>0</v>
       </c>
       <c r="AF13">
-        <v>82</v>
+        <v>0.011</v>
       </c>
       <c r="AG13">
-        <v>68</v>
+        <v>-1.459</v>
       </c>
       <c r="AH13">
-        <v>0.6259541984732825</v>
+        <v>0.0005816720427264555</v>
       </c>
       <c r="AI13">
-        <v>0.5521885521885522</v>
+        <v>0.0003037750959653144</v>
       </c>
       <c r="AJ13">
-        <v>0.5811965811965812</v>
+        <v>-0.08365346023737172</v>
       </c>
       <c r="AK13">
-        <v>0.5055762081784386</v>
+        <v>-0.04199648829912783</v>
       </c>
       <c r="AL13">
-        <v>6.22</v>
+        <v>0.004</v>
       </c>
       <c r="AM13">
-        <v>6.22</v>
+        <v>-2.086</v>
       </c>
       <c r="AN13">
-        <v>11.63120567375887</v>
+        <v>-0.01381909547738693</v>
       </c>
       <c r="AO13">
-        <v>1.014469453376206</v>
+        <v>-200.75</v>
       </c>
       <c r="AP13">
-        <v>9.645390070921986</v>
+        <v>1.832914572864322</v>
       </c>
       <c r="AQ13">
-        <v>1.014469453376206</v>
+        <v>0.3849472674976031</v>
       </c>
     </row>
     <row r="14">
@@ -2157,7 +2085,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>PSG Konsult Limited (JSE:KST)</t>
+          <t>RH Bophelo Limited (JSE:RHB)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2165,110 +2093,116 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="D14">
-        <v>0.08900000000000001</v>
-      </c>
-      <c r="E14">
-        <v>0.196</v>
-      </c>
       <c r="G14">
-        <v>0</v>
+        <v>13.37579617834395</v>
       </c>
       <c r="H14">
-        <v>0</v>
+        <v>13.37579617834395</v>
       </c>
       <c r="I14">
-        <v>0</v>
+        <v>-3.821656050955414</v>
       </c>
       <c r="J14">
-        <v>0</v>
+        <v>-3.821656050955414</v>
       </c>
       <c r="K14">
-        <v>53.6</v>
+        <v>-0.784</v>
       </c>
       <c r="L14">
-        <v>0.1404980340760157</v>
+        <v>-2.496815286624204</v>
       </c>
       <c r="M14">
-        <v>35</v>
+        <v>0.229</v>
       </c>
       <c r="N14">
-        <v>0.0311804008908686</v>
+        <v>0.02729439809296782</v>
       </c>
       <c r="O14">
-        <v>0.6529850746268656</v>
+        <v>-0.2920918367346939</v>
       </c>
       <c r="P14">
-        <v>22.4</v>
+        <v>0.229</v>
       </c>
       <c r="Q14">
-        <v>0.0199554565701559</v>
+        <v>0.02729439809296782</v>
       </c>
       <c r="R14">
-        <v>0.417910447761194</v>
+        <v>-0.2920918367346939</v>
       </c>
       <c r="S14">
-        <v>12.6</v>
+        <v>0</v>
       </c>
       <c r="T14">
-        <v>0.36</v>
+        <v>0</v>
       </c>
       <c r="U14">
-        <v>115.7</v>
+        <v>2.48</v>
       </c>
       <c r="V14">
-        <v>0.1030734966592428</v>
+        <v>0.2955899880810489</v>
       </c>
       <c r="W14">
-        <v>0.2637795275590551</v>
+        <v>-0.01226917057902973</v>
       </c>
       <c r="X14">
-        <v>0.06589310221348783</v>
+        <v>0.1192733492156979</v>
       </c>
       <c r="Y14">
-        <v>0.1978864253455673</v>
+        <v>-0.1315425197947276</v>
       </c>
       <c r="Z14">
-        <v>3.032591414944356</v>
+        <v>0.004978516275308779</v>
       </c>
       <c r="AA14">
-        <v>0</v>
+        <v>-0.0190261768483138</v>
       </c>
       <c r="AB14">
-        <v>0.06535076575439164</v>
+        <v>0.105799771629851</v>
       </c>
       <c r="AC14">
-        <v>-0.06535076575439164</v>
+        <v>-0.1248259484781648</v>
       </c>
       <c r="AD14">
-        <v>20.2</v>
+        <v>3.14</v>
       </c>
       <c r="AE14">
         <v>0</v>
       </c>
       <c r="AF14">
-        <v>20.2</v>
+        <v>3.14</v>
       </c>
       <c r="AG14">
-        <v>-95.5</v>
+        <v>0.6600000000000001</v>
       </c>
       <c r="AH14">
-        <v>0.01767743064671392</v>
+        <v>0.2723330442324371</v>
       </c>
       <c r="AI14">
-        <v>0.06633825944170771</v>
+        <v>0.0556343019135365</v>
       </c>
       <c r="AJ14">
-        <v>-0.09298928919182084</v>
+        <v>0.07292817679558013</v>
       </c>
       <c r="AK14">
-        <v>-0.5058262711864406</v>
+        <v>0.01223128243143069</v>
       </c>
       <c r="AL14">
-        <v>0</v>
+        <v>0.068</v>
       </c>
       <c r="AM14">
-        <v>0</v>
+        <v>0.068</v>
+      </c>
+      <c r="AN14">
+        <v>-2.638655462184874</v>
+      </c>
+      <c r="AO14">
+        <v>-17.64705882352941</v>
+      </c>
+      <c r="AP14">
+        <v>-0.5546218487394959</v>
+      </c>
+      <c r="AQ14">
+        <v>-17.64705882352941</v>
       </c>
     </row>
     <row r="15">
@@ -2279,7 +2213,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Purple Group Limited (JSE:PPE)</t>
+          <t>African Equity Empowerment Investments Limited (JSE:AEE)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2288,433 +2222,109 @@
         </is>
       </c>
       <c r="D15">
-        <v>0.137</v>
+        <v>0.26</v>
       </c>
       <c r="G15">
-        <v>0.08749999999999999</v>
+        <v>-0.1730192188468692</v>
       </c>
       <c r="H15">
-        <v>0</v>
+        <v>-0.1735895846249225</v>
       </c>
       <c r="I15">
-        <v>0</v>
+        <v>-0.2145071295722256</v>
       </c>
       <c r="J15">
-        <v>0</v>
+        <v>-0.2145071295722256</v>
       </c>
       <c r="K15">
-        <v>3.06</v>
+        <v>-9.18</v>
       </c>
       <c r="L15">
-        <v>0.225</v>
+        <v>-0.0569125852448853</v>
       </c>
       <c r="M15">
-        <v>-0</v>
+        <v>16.8</v>
       </c>
       <c r="N15">
-        <v>-0</v>
+        <v>0.6774193548387097</v>
       </c>
       <c r="O15">
-        <v>-0</v>
+        <v>-1.830065359477124</v>
       </c>
       <c r="P15">
-        <v>-0</v>
+        <v>16.8</v>
       </c>
       <c r="Q15">
-        <v>-0</v>
+        <v>0.6774193548387097</v>
       </c>
       <c r="R15">
-        <v>-0</v>
+        <v>-1.830065359477124</v>
       </c>
       <c r="S15">
         <v>0</v>
       </c>
+      <c r="T15">
+        <v>0</v>
+      </c>
       <c r="U15">
-        <v>17.8</v>
+        <v>161.7</v>
       </c>
       <c r="V15">
-        <v>0.08644973288003885</v>
+        <v>6.52016129032258</v>
       </c>
       <c r="W15">
-        <v>0.1738636363636364</v>
+        <v>-0.04870026525198939</v>
       </c>
       <c r="X15">
-        <v>0.06584658655825346</v>
+        <v>0.130284539896026</v>
       </c>
       <c r="Y15">
-        <v>0.1080170498053829</v>
-      </c>
-      <c r="Z15">
-        <v>-4.738675958188154</v>
-      </c>
-      <c r="AA15">
-        <v>-0</v>
+        <v>-0.1789848051480153</v>
       </c>
       <c r="AB15">
-        <v>0.06539784108361341</v>
-      </c>
-      <c r="AC15">
-        <v>-0.06539784108361341</v>
+        <v>0.1072999266621416</v>
       </c>
       <c r="AD15">
-        <v>3.44</v>
+        <v>15.2</v>
       </c>
       <c r="AE15">
         <v>0</v>
       </c>
       <c r="AF15">
-        <v>3.44</v>
+        <v>15.2</v>
       </c>
       <c r="AG15">
-        <v>-14.36</v>
+        <v>-146.5</v>
       </c>
       <c r="AH15">
-        <v>0.01643259768797172</v>
+        <v>0.38</v>
       </c>
       <c r="AI15">
-        <v>0.1001747233546884</v>
+        <v>0.0391147709727226</v>
       </c>
       <c r="AJ15">
-        <v>-0.07497128537120185</v>
+        <v>1.203779786359901</v>
       </c>
       <c r="AK15">
-        <v>-0.8681983071342202</v>
+        <v>-0.6456588805641252</v>
       </c>
       <c r="AL15">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AM15">
-        <v>-0.296</v>
+        <v>-9.68</v>
+      </c>
+      <c r="AN15">
+        <v>-0.5428571428571428</v>
+      </c>
+      <c r="AO15">
+        <v>-22.76315789473684</v>
+      </c>
+      <c r="AP15">
+        <v>5.232142857142857</v>
       </c>
       <c r="AQ15">
-        <v>-0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>South Africa</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Zeder Investments Ltd. (JSE:ZED)</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Investments &amp; Asset Management</t>
-        </is>
-      </c>
-      <c r="E16">
-        <v>0.0796</v>
-      </c>
-      <c r="K16">
-        <v>94.09999999999999</v>
-      </c>
-      <c r="M16">
-        <v>11.3</v>
-      </c>
-      <c r="N16">
-        <v>0.0361947469570788</v>
-      </c>
-      <c r="O16">
-        <v>0.1200850159404889</v>
-      </c>
-      <c r="P16">
-        <v>-0</v>
-      </c>
-      <c r="Q16">
-        <v>-0</v>
-      </c>
-      <c r="R16">
-        <v>-0</v>
-      </c>
-      <c r="S16">
-        <v>11.3</v>
-      </c>
-      <c r="T16">
-        <v>1</v>
-      </c>
-      <c r="U16">
-        <v>32.8</v>
-      </c>
-      <c r="V16">
-        <v>0.1050608584240871</v>
-      </c>
-      <c r="W16">
-        <v>0.2693188322839153</v>
-      </c>
-      <c r="X16">
-        <v>0.06524340450733665</v>
-      </c>
-      <c r="Y16">
-        <v>0.2040754277765786</v>
-      </c>
-      <c r="Z16">
-        <v>0</v>
-      </c>
-      <c r="AA16">
-        <v>-0.005229755206430399</v>
-      </c>
-      <c r="AB16">
-        <v>0.06524340450733665</v>
-      </c>
-      <c r="AC16">
-        <v>-0.07047315971376705</v>
-      </c>
-      <c r="AD16">
-        <v>0</v>
-      </c>
-      <c r="AE16">
-        <v>0</v>
-      </c>
-      <c r="AF16">
-        <v>0</v>
-      </c>
-      <c r="AG16">
-        <v>-32.8</v>
-      </c>
-      <c r="AH16">
-        <v>0</v>
-      </c>
-      <c r="AI16">
-        <v>0</v>
-      </c>
-      <c r="AJ16">
-        <v>-0.117394416607015</v>
-      </c>
-      <c r="AK16">
-        <v>-0.07468123861566484</v>
-      </c>
-      <c r="AL16">
-        <v>0.138</v>
-      </c>
-      <c r="AM16">
-        <v>-10.562</v>
-      </c>
-      <c r="AO16">
-        <v>-11.01449275362319</v>
-      </c>
-      <c r="AQ16">
-        <v>0.1439121378526794</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>South Africa</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>MTN Zakhele Futhi (RF) Limited (JSE:MTNZF)</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Investments &amp; Asset Management</t>
-        </is>
-      </c>
-      <c r="K17">
-        <v>-8.56</v>
-      </c>
-      <c r="M17">
-        <v>-0</v>
-      </c>
-      <c r="N17">
-        <v>-0</v>
-      </c>
-      <c r="O17">
-        <v>0</v>
-      </c>
-      <c r="P17">
-        <v>-0</v>
-      </c>
-      <c r="Q17">
-        <v>-0</v>
-      </c>
-      <c r="R17">
-        <v>0</v>
-      </c>
-      <c r="S17">
-        <v>0</v>
-      </c>
-      <c r="U17">
-        <v>0.127</v>
-      </c>
-      <c r="V17">
-        <v>0.0005298289528577389</v>
-      </c>
-      <c r="W17">
-        <v>-0.1606003752345216</v>
-      </c>
-      <c r="X17">
-        <v>0.07554570899284903</v>
-      </c>
-      <c r="Y17">
-        <v>-0.2361460842273706</v>
-      </c>
-      <c r="Z17">
-        <v>0</v>
-      </c>
-      <c r="AA17">
-        <v>-0.01096960118992284</v>
-      </c>
-      <c r="AB17">
-        <v>0.06732985625665545</v>
-      </c>
-      <c r="AC17">
-        <v>-0.07829945744657829</v>
-      </c>
-      <c r="AD17">
-        <v>68.40000000000001</v>
-      </c>
-      <c r="AE17">
-        <v>0</v>
-      </c>
-      <c r="AF17">
-        <v>68.40000000000001</v>
-      </c>
-      <c r="AG17">
-        <v>68.27300000000001</v>
-      </c>
-      <c r="AH17">
-        <v>0.2220058422590068</v>
-      </c>
-      <c r="AI17">
-        <v>0.224188790560472</v>
-      </c>
-      <c r="AJ17">
-        <v>0.2216850178424732</v>
-      </c>
-      <c r="AK17">
-        <v>0.2238657192603936</v>
-      </c>
-      <c r="AL17">
-        <v>3.41</v>
-      </c>
-      <c r="AM17">
-        <v>3.392</v>
-      </c>
-      <c r="AO17">
-        <v>-0.346041055718475</v>
-      </c>
-      <c r="AQ17">
-        <v>-0.347877358490566</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>South Africa</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Mahube Infrastructure Limited (JSE:MHB)</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Investments &amp; Asset Management</t>
-        </is>
-      </c>
-      <c r="K18">
-        <v>1.1</v>
-      </c>
-      <c r="M18">
-        <v>1.9</v>
-      </c>
-      <c r="N18">
-        <v>0.08837209302325581</v>
-      </c>
-      <c r="O18">
-        <v>1.727272727272727</v>
-      </c>
-      <c r="P18">
-        <v>1.9</v>
-      </c>
-      <c r="Q18">
-        <v>0.08837209302325581</v>
-      </c>
-      <c r="R18">
-        <v>1.727272727272727</v>
-      </c>
-      <c r="S18">
-        <v>0</v>
-      </c>
-      <c r="T18">
-        <v>0</v>
-      </c>
-      <c r="U18">
-        <v>0.06900000000000001</v>
-      </c>
-      <c r="V18">
-        <v>0.003209302325581395</v>
-      </c>
-      <c r="W18">
-        <v>0.03047091412742382</v>
-      </c>
-      <c r="X18">
-        <v>0.06534751620860213</v>
-      </c>
-      <c r="Y18">
-        <v>-0.03487660208117831</v>
-      </c>
-      <c r="Z18">
-        <v>0</v>
-      </c>
-      <c r="AA18">
-        <v>-0.023729196509668</v>
-      </c>
-      <c r="AB18">
-        <v>0.06527042831804616</v>
-      </c>
-      <c r="AC18">
-        <v>-0.08899962482771417</v>
-      </c>
-      <c r="AD18">
-        <v>0.062</v>
-      </c>
-      <c r="AE18">
-        <v>0</v>
-      </c>
-      <c r="AF18">
-        <v>0.062</v>
-      </c>
-      <c r="AG18">
-        <v>-0.007000000000000006</v>
-      </c>
-      <c r="AH18">
-        <v>0.002875428995454967</v>
-      </c>
-      <c r="AI18">
-        <v>0.00149174726914008</v>
-      </c>
-      <c r="AJ18">
-        <v>-0.0003256874331177596</v>
-      </c>
-      <c r="AK18">
-        <v>-0.0001687031547489939</v>
-      </c>
-      <c r="AL18">
-        <v>0.011</v>
-      </c>
-      <c r="AM18">
-        <v>-4.059</v>
-      </c>
-      <c r="AN18">
-        <v>-0.07242990654205607</v>
-      </c>
-      <c r="AO18">
-        <v>-78.54545454545455</v>
-      </c>
-      <c r="AP18">
-        <v>0.008177570093457952</v>
-      </c>
-      <c r="AQ18">
-        <v>0.212860310421286</v>
+        <v>3.574380165289257</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/south_africa/south_africa_investments_asset_management.xlsx
+++ b/research/traditional_assets/database/data/south_africa/south_africa_investments_asset_management.xlsx
@@ -588,124 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.227</v>
+        <v>0.08025</v>
       </c>
       <c r="E2">
-        <v>0.08985</v>
+        <v>-0.153</v>
       </c>
       <c r="F2">
-        <v>-0.0277</v>
+        <v>-0.0215</v>
       </c>
       <c r="G2">
-        <v>0.2828576927103215</v>
+        <v>0.2358660478080121</v>
       </c>
       <c r="H2">
-        <v>0.2827339757451303</v>
+        <v>0.2352838010204082</v>
       </c>
       <c r="I2">
-        <v>0.2631983267544811</v>
+        <v>0.2538554657974301</v>
       </c>
       <c r="J2">
-        <v>0.2312737334138957</v>
+        <v>0.2157710284356447</v>
       </c>
       <c r="K2">
-        <v>372.156</v>
+        <v>153.78</v>
       </c>
       <c r="L2">
-        <v>0.1967607303319104</v>
+        <v>0.09080924036281181</v>
       </c>
       <c r="M2">
-        <v>380.63</v>
+        <v>324.2292</v>
       </c>
       <c r="N2">
-        <v>0.07733097119313137</v>
+        <v>0.0662638871857756</v>
       </c>
       <c r="O2">
-        <v>1.022770021173916</v>
+        <v>2.108396410456496</v>
       </c>
       <c r="P2">
-        <v>321.617</v>
+        <v>257.6652</v>
       </c>
       <c r="Q2">
-        <v>0.06534155206426538</v>
+        <v>0.05265996321275292</v>
       </c>
       <c r="R2">
-        <v>0.8641994217478692</v>
+        <v>1.675544284042138</v>
       </c>
       <c r="S2">
-        <v>59.01300000000001</v>
+        <v>66.56399999999999</v>
       </c>
       <c r="T2">
-        <v>0.1550403278774663</v>
+        <v>0.2052992142595423</v>
       </c>
       <c r="U2">
-        <v>891.671</v>
+        <v>840.158</v>
       </c>
       <c r="V2">
-        <v>0.1811569881899762</v>
+        <v>0.1717061107704884</v>
       </c>
       <c r="W2">
-        <v>0.106711915535445</v>
+        <v>0.01654320987654321</v>
       </c>
       <c r="X2">
-        <v>0.1047547349684686</v>
+        <v>0.08673205298478559</v>
       </c>
       <c r="Y2">
-        <v>0.001957180566976399</v>
+        <v>-0.07018884310824239</v>
       </c>
       <c r="Z2">
-        <v>0.7552270356020988</v>
+        <v>0.9186797233935554</v>
       </c>
       <c r="AA2">
-        <v>0.04328252009194256</v>
+        <v>0.03649952203006866</v>
       </c>
       <c r="AB2">
-        <v>0.1023167409492499</v>
+        <v>0.08510159772150479</v>
       </c>
       <c r="AC2">
-        <v>-0.06177038888978877</v>
+        <v>-0.04970063324005285</v>
       </c>
       <c r="AD2">
-        <v>793.831</v>
+        <v>728.6610000000001</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>793.831</v>
+        <v>728.6610000000001</v>
       </c>
       <c r="AG2">
-        <v>-97.84000000000003</v>
+        <v>-111.497</v>
       </c>
       <c r="AH2">
-        <v>0.138880680821166</v>
+        <v>0.1296166737908956</v>
       </c>
       <c r="AI2">
-        <v>0.2401232814598974</v>
+        <v>0.2785655876052897</v>
       </c>
       <c r="AJ2">
-        <v>-0.020280872674509</v>
+        <v>-0.02331840009302514</v>
       </c>
       <c r="AK2">
-        <v>-0.04052587542352524</v>
+        <v>-0.06279387903714961</v>
       </c>
       <c r="AL2">
-        <v>45.192</v>
+        <v>50.915</v>
       </c>
       <c r="AM2">
-        <v>-405.172</v>
+        <v>-1263.97</v>
       </c>
       <c r="AN2">
-        <v>1.753493375508599</v>
+        <v>1.88952910943363</v>
       </c>
       <c r="AO2">
-        <v>11.01560010621349</v>
+        <v>8.443268192084847</v>
       </c>
       <c r="AP2">
-        <v>-0.2161187858117929</v>
+        <v>-0.2891287266843173</v>
       </c>
       <c r="AQ2">
-        <v>-1.22865597820185</v>
+        <v>-0.3401101291961043</v>
       </c>
     </row>
     <row r="3">
@@ -725,118 +725,118 @@
         </is>
       </c>
       <c r="F3">
-        <v>-0.0277</v>
+        <v>-0.0215</v>
       </c>
       <c r="G3">
-        <v>0.4524295630869742</v>
+        <v>0.3448512272041684</v>
       </c>
       <c r="H3">
-        <v>0.4524295630869742</v>
+        <v>0.3448512272041684</v>
       </c>
       <c r="I3">
-        <v>0.3615080985436233</v>
+        <v>0.3134512546277252</v>
       </c>
       <c r="J3">
-        <v>0.2776361063714637</v>
+        <v>0.2410108493219542</v>
       </c>
       <c r="K3">
-        <v>210.2</v>
+        <v>193.3</v>
       </c>
       <c r="L3">
-        <v>0.2861031713624608</v>
+        <v>0.2650486768133827</v>
       </c>
       <c r="M3">
-        <v>180.4</v>
+        <v>186.4</v>
       </c>
       <c r="N3">
-        <v>0.08833178279390884</v>
+        <v>0.08848801329219085</v>
       </c>
       <c r="O3">
-        <v>0.8582302568981923</v>
+        <v>0.9643041903776512</v>
       </c>
       <c r="P3">
-        <v>148.6</v>
+        <v>148.8</v>
       </c>
       <c r="Q3">
-        <v>0.07276110267835284</v>
+        <v>0.07063849988131973</v>
       </c>
       <c r="R3">
-        <v>0.7069457659372027</v>
+        <v>0.7697878944645629</v>
       </c>
       <c r="S3">
-        <v>31.80000000000001</v>
+        <v>37.59999999999999</v>
       </c>
       <c r="T3">
-        <v>0.1762749445676275</v>
+        <v>0.2017167381974249</v>
       </c>
       <c r="U3">
-        <v>363.1</v>
+        <v>389.9</v>
       </c>
       <c r="V3">
-        <v>0.1777897468540371</v>
+        <v>0.1850937574175172</v>
       </c>
       <c r="W3">
-        <v>0.5430121415654869</v>
+        <v>0.5124602332979852</v>
       </c>
       <c r="X3">
-        <v>0.1047547349684686</v>
+        <v>0.08673205298478559</v>
       </c>
       <c r="Y3">
-        <v>0.4382574065970184</v>
+        <v>0.4257281803131996</v>
       </c>
       <c r="Z3">
-        <v>5.882305844675742</v>
+        <v>5.370397643593521</v>
       </c>
       <c r="AA3">
-        <v>1.633140491201877</v>
+        <v>1.294324097279096</v>
       </c>
       <c r="AB3">
-        <v>0.1023167409492499</v>
+        <v>0.08510159772150479</v>
       </c>
       <c r="AC3">
-        <v>1.530823750252627</v>
+        <v>1.209222499557591</v>
       </c>
       <c r="AD3">
-        <v>121.7</v>
+        <v>121.4</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>121.7</v>
+        <v>121.4</v>
       </c>
       <c r="AG3">
-        <v>-241.4</v>
+        <v>-268.5</v>
       </c>
       <c r="AH3">
-        <v>0.05623844731977819</v>
+        <v>0.05449077606714844</v>
       </c>
       <c r="AI3">
-        <v>0.2438877755511022</v>
+        <v>0.2275112443778111</v>
       </c>
       <c r="AJ3">
-        <v>-0.1340440890665779</v>
+        <v>-0.1460826985854189</v>
       </c>
       <c r="AK3">
-        <v>-1.776306107431936</v>
+        <v>-1.868475991649269</v>
       </c>
       <c r="AL3">
-        <v>4.23</v>
+        <v>4.76</v>
       </c>
       <c r="AM3">
-        <v>-3.35</v>
+        <v>-21.34</v>
       </c>
       <c r="AN3">
-        <v>0.4485809067453004</v>
+        <v>0.5190252244548953</v>
       </c>
       <c r="AO3">
-        <v>62.78959810874704</v>
+        <v>48.02521008403362</v>
       </c>
       <c r="AP3">
-        <v>-0.8897899004791744</v>
+        <v>-1.147926464300983</v>
       </c>
       <c r="AQ3">
-        <v>-79.28358208955225</v>
+        <v>-10.71227741330834</v>
       </c>
     </row>
     <row r="4">
@@ -847,7 +847,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Coronation Fund Managers Limited (JSE:CML)</t>
+          <t>Alexander Forbes Group Holdings Limited (JSE:AFH)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -856,121 +856,118 @@
         </is>
       </c>
       <c r="D4">
-        <v>-0.0103</v>
-      </c>
-      <c r="E4">
-        <v>-0.034</v>
+        <v>0.0646</v>
       </c>
       <c r="G4">
-        <v>0.5024177949709865</v>
+        <v>0.1828177882723337</v>
       </c>
       <c r="H4">
-        <v>0.5024177949709865</v>
+        <v>0.1790633608815427</v>
       </c>
       <c r="I4">
-        <v>0.5</v>
+        <v>0.170405352223534</v>
       </c>
       <c r="J4">
-        <v>0.3785942492012779</v>
+        <v>0.121861587837655</v>
       </c>
       <c r="K4">
-        <v>71.09999999999999</v>
+        <v>46.1</v>
       </c>
       <c r="L4">
-        <v>0.3438104448742746</v>
+        <v>0.1814246359700905</v>
       </c>
       <c r="M4">
-        <v>85.40000000000001</v>
+        <v>37.31</v>
       </c>
       <c r="N4">
-        <v>0.1351052048726467</v>
+        <v>0.08374859708193041</v>
       </c>
       <c r="O4">
-        <v>1.20112517580872</v>
+        <v>0.8093275488069415</v>
       </c>
       <c r="P4">
-        <v>85.40000000000001</v>
+        <v>28.3</v>
       </c>
       <c r="Q4">
-        <v>0.1351052048726467</v>
+        <v>0.06352413019079686</v>
       </c>
       <c r="R4">
-        <v>1.20112517580872</v>
+        <v>0.613882863340564</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>9.010000000000002</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>0.2414902170999732</v>
       </c>
       <c r="U4">
-        <v>36.4</v>
+        <v>141.1</v>
       </c>
       <c r="V4">
-        <v>0.05758582502768549</v>
+        <v>0.31672278338945</v>
       </c>
       <c r="W4">
-        <v>0.4708609271523179</v>
+        <v>0.204162976085031</v>
       </c>
       <c r="X4">
-        <v>0.1043848982070629</v>
+        <v>0.08714850207691049</v>
       </c>
       <c r="Y4">
-        <v>0.3664760289452549</v>
+        <v>0.1170144740081205</v>
       </c>
       <c r="Z4">
-        <v>2.764705882352941</v>
+        <v>7.818461538461531</v>
       </c>
       <c r="AA4">
-        <v>1.046701747791768</v>
+        <v>0.952770137524557</v>
       </c>
       <c r="AB4">
-        <v>0.1022768997820443</v>
+        <v>0.08516287284418038</v>
       </c>
       <c r="AC4">
-        <v>0.944424848009724</v>
+        <v>0.8676072646803766</v>
       </c>
       <c r="AD4">
-        <v>32.6</v>
+        <v>31.2</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>32.6</v>
+        <v>31.2</v>
       </c>
       <c r="AG4">
-        <v>-3.799999999999997</v>
+        <v>-109.9</v>
       </c>
       <c r="AH4">
-        <v>0.04904468181134346</v>
+        <v>0.06544996853366897</v>
       </c>
       <c r="AI4">
-        <v>0.2235939643347051</v>
+        <v>0.1171610965076981</v>
       </c>
       <c r="AJ4">
-        <v>-0.006048066210409035</v>
+        <v>-0.3274731823599523</v>
       </c>
       <c r="AK4">
-        <v>-0.03473491773308955</v>
+        <v>-0.8777955271565494</v>
       </c>
       <c r="AL4">
-        <v>3.33</v>
+        <v>3.07</v>
       </c>
       <c r="AM4">
-        <v>-159.77</v>
+        <v>-9.129999999999999</v>
       </c>
       <c r="AN4">
-        <v>0.3137632338787296</v>
+        <v>0.6582278481012658</v>
       </c>
       <c r="AO4">
-        <v>31.05105105105105</v>
+        <v>14.1042345276873</v>
       </c>
       <c r="AP4">
-        <v>-0.03657362848893164</v>
+        <v>-2.318565400843882</v>
       </c>
       <c r="AQ4">
-        <v>-0.6471803217124618</v>
+        <v>-4.742606790799562</v>
       </c>
     </row>
     <row r="5">
@@ -981,7 +978,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Sygnia Limited (JSE:SYG)</t>
+          <t>Coronation Fund Managers Limited (JSE:CML)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -990,121 +987,121 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.194</v>
+        <v>-0.0108</v>
       </c>
       <c r="E5">
-        <v>0.254</v>
+        <v>-0.153</v>
       </c>
       <c r="G5">
-        <v>0.4810690423162584</v>
+        <v>0.4340403517847905</v>
       </c>
       <c r="H5">
-        <v>0.4810690423162584</v>
+        <v>0.4340403517847905</v>
       </c>
       <c r="I5">
-        <v>0.4699331848552339</v>
+        <v>0.4304190377651319</v>
       </c>
       <c r="J5">
-        <v>0.3354859328652612</v>
+        <v>0.215209518882566</v>
       </c>
       <c r="K5">
-        <v>15.9</v>
+        <v>33.9</v>
       </c>
       <c r="L5">
-        <v>0.3541202672605791</v>
+        <v>0.1753750646663218</v>
       </c>
       <c r="M5">
-        <v>13.593</v>
+        <v>31.9</v>
       </c>
       <c r="N5">
-        <v>0.08532956685499057</v>
+        <v>0.05353247189125692</v>
       </c>
       <c r="O5">
-        <v>0.8549056603773585</v>
+        <v>0.9410029498525073</v>
       </c>
       <c r="P5">
-        <v>13.3</v>
+        <v>31.9</v>
       </c>
       <c r="Q5">
-        <v>0.08349026993094789</v>
+        <v>0.05353247189125692</v>
       </c>
       <c r="R5">
-        <v>0.8364779874213837</v>
+        <v>0.9410029498525073</v>
       </c>
       <c r="S5">
-        <v>0.2929999999999993</v>
+        <v>0</v>
       </c>
       <c r="T5">
-        <v>0.02155521224159488</v>
+        <v>0</v>
       </c>
       <c r="U5">
-        <v>19.8</v>
+        <v>60.5</v>
       </c>
       <c r="V5">
-        <v>0.1242937853107345</v>
+        <v>0.1015271018627286</v>
       </c>
       <c r="W5">
-        <v>0.3057692307692308</v>
+        <v>0.2994699646643109</v>
       </c>
       <c r="X5">
-        <v>0.1045628083187847</v>
+        <v>0.08665641161411664</v>
       </c>
       <c r="Y5">
-        <v>0.2012064224504461</v>
+        <v>0.2128135530501943</v>
       </c>
       <c r="Z5">
-        <v>1.83115823817292</v>
+        <v>3.944897959183673</v>
       </c>
       <c r="AA5">
-        <v>0.6143278297573501</v>
+        <v>0.8489795918367345</v>
       </c>
       <c r="AB5">
-        <v>0.1022961409260572</v>
+        <v>0.08509031351841287</v>
       </c>
       <c r="AC5">
-        <v>0.5120316888312929</v>
+        <v>0.7638892783183217</v>
       </c>
       <c r="AD5">
-        <v>8.83</v>
+        <v>33</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>8.83</v>
+        <v>33</v>
       </c>
       <c r="AG5">
-        <v>-10.97</v>
+        <v>-27.5</v>
       </c>
       <c r="AH5">
-        <v>0.0525188841967525</v>
+        <v>0.05247257115598664</v>
       </c>
       <c r="AI5">
-        <v>0.1590131460471817</v>
+        <v>0.2309307207837649</v>
       </c>
       <c r="AJ5">
-        <v>-0.07395671812849727</v>
+        <v>-0.04838142153413089</v>
       </c>
       <c r="AK5">
-        <v>-0.3070249090400224</v>
+        <v>-0.3337378640776699</v>
       </c>
       <c r="AL5">
-        <v>0.63</v>
+        <v>3.07</v>
       </c>
       <c r="AM5">
-        <v>-256.37</v>
+        <v>-175.93</v>
       </c>
       <c r="AN5">
-        <v>0.4087962962962963</v>
+        <v>0.3933253873659118</v>
       </c>
       <c r="AO5">
-        <v>33.49206349206349</v>
+        <v>27.10097719869707</v>
       </c>
       <c r="AP5">
-        <v>-0.5078703703703704</v>
+        <v>-0.3277711561382598</v>
       </c>
       <c r="AQ5">
-        <v>-0.08230292155868471</v>
+        <v>-0.4729153640652532</v>
       </c>
     </row>
     <row r="6">
@@ -1115,7 +1112,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Alexander Forbes Group Holdings Limited (JSE:AFH)</t>
+          <t>Sygnia Limited (JSE:SYG)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1124,121 +1121,121 @@
         </is>
       </c>
       <c r="D6">
-        <v>-0.0279</v>
+        <v>0.149</v>
       </c>
       <c r="E6">
-        <v>-0.183</v>
+        <v>0.243</v>
       </c>
       <c r="G6">
-        <v>0.2232415519399249</v>
+        <v>0.4630872483221476</v>
       </c>
       <c r="H6">
-        <v>0.2227784730913642</v>
+        <v>0.4630872483221476</v>
       </c>
       <c r="I6">
-        <v>0.1330830204422195</v>
+        <v>0.4519015659955257</v>
       </c>
       <c r="J6">
-        <v>0.09473968063944666</v>
+        <v>0.3236263681142845</v>
       </c>
       <c r="K6">
-        <v>28.3</v>
+        <v>15.9</v>
       </c>
       <c r="L6">
-        <v>0.1180642469753859</v>
+        <v>0.3557046979865772</v>
       </c>
       <c r="M6">
-        <v>31.79</v>
+        <v>17.308</v>
       </c>
       <c r="N6">
-        <v>0.08328530259365995</v>
+        <v>0.1155407209612817</v>
       </c>
       <c r="O6">
-        <v>1.123321554770318</v>
+        <v>1.088553459119497</v>
       </c>
       <c r="P6">
-        <v>23.3</v>
+        <v>17.3</v>
       </c>
       <c r="Q6">
-        <v>0.06104270369400053</v>
+        <v>0.1154873164218959</v>
       </c>
       <c r="R6">
-        <v>0.823321554770318</v>
+        <v>1.088050314465409</v>
       </c>
       <c r="S6">
-        <v>8.489999999999998</v>
+        <v>0.007999999999999119</v>
       </c>
       <c r="T6">
-        <v>0.2670651148159798</v>
+        <v>0.0004622140050843032</v>
       </c>
       <c r="U6">
-        <v>149.2</v>
+        <v>57.5</v>
       </c>
       <c r="V6">
-        <v>0.3908828923238145</v>
+        <v>0.383845126835781</v>
       </c>
       <c r="W6">
-        <v>0.106711915535445</v>
+        <v>0.3404710920770878</v>
       </c>
       <c r="X6">
-        <v>0.106236071980911</v>
+        <v>0.08682773277705072</v>
       </c>
       <c r="Y6">
-        <v>0.0004758435545339085</v>
+        <v>0.253643359300037</v>
       </c>
       <c r="Z6">
-        <v>4.183246073298427</v>
+        <v>1.63019693654267</v>
       </c>
       <c r="AA6">
-        <v>0.3963193970205123</v>
+        <v>0.527574713884337</v>
       </c>
       <c r="AB6">
-        <v>0.1024704552939412</v>
+        <v>0.08511580258917228</v>
       </c>
       <c r="AC6">
-        <v>0.2938489417265711</v>
+        <v>0.4424589112951647</v>
       </c>
       <c r="AD6">
-        <v>35</v>
+        <v>9.06</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>35</v>
+        <v>9.06</v>
       </c>
       <c r="AG6">
-        <v>-114.2</v>
+        <v>-48.44</v>
       </c>
       <c r="AH6">
-        <v>0.083993280537557</v>
+        <v>0.05703134835704394</v>
       </c>
       <c r="AI6">
-        <v>0.1332825590251333</v>
+        <v>0.1723744292237443</v>
       </c>
       <c r="AJ6">
-        <v>-0.4269158878504672</v>
+        <v>-0.4779005524861877</v>
       </c>
       <c r="AK6">
-        <v>-1.00705467372134</v>
+        <v>9.805668016194335</v>
       </c>
       <c r="AL6">
-        <v>3.27</v>
+        <v>0.698</v>
       </c>
       <c r="AM6">
-        <v>-3.33</v>
+        <v>-1088.502</v>
       </c>
       <c r="AN6">
-        <v>0.925925925925926</v>
+        <v>0.4376811594202899</v>
       </c>
       <c r="AO6">
-        <v>9.755351681957187</v>
+        <v>28.93982808022923</v>
       </c>
       <c r="AP6">
-        <v>-3.021164021164021</v>
+        <v>-2.340096618357488</v>
       </c>
       <c r="AQ6">
-        <v>-9.57957957957958</v>
+        <v>-0.01855761404205045</v>
       </c>
     </row>
     <row r="7">
@@ -1249,7 +1246,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Sabvest Capital Limited (JSE:SBP)</t>
+          <t>Trencor Limited (JSE:TRE)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1257,122 +1254,92 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="D7">
-        <v>0.507</v>
-      </c>
       <c r="E7">
-        <v>1.769</v>
-      </c>
-      <c r="G7">
-        <v>0.8858195211786373</v>
-      </c>
-      <c r="H7">
-        <v>0.8858195211786373</v>
-      </c>
-      <c r="I7">
-        <v>0.8839779005524863</v>
-      </c>
-      <c r="J7">
-        <v>0.8067721053754773</v>
+        <v>-0.528</v>
       </c>
       <c r="K7">
-        <v>42.6</v>
-      </c>
-      <c r="L7">
-        <v>0.7845303867403316</v>
+        <v>6.11</v>
       </c>
       <c r="M7">
-        <v>5.008</v>
+        <v>-0</v>
       </c>
       <c r="N7">
-        <v>0.02562947799385875</v>
+        <v>-0</v>
       </c>
       <c r="O7">
-        <v>0.1175586854460094</v>
+        <v>-0</v>
       </c>
       <c r="P7">
-        <v>0.878</v>
+        <v>-0</v>
       </c>
       <c r="Q7">
-        <v>0.004493346980552712</v>
+        <v>-0</v>
       </c>
       <c r="R7">
-        <v>0.02061032863849765</v>
+        <v>-0</v>
       </c>
       <c r="S7">
-        <v>4.13</v>
-      </c>
-      <c r="T7">
-        <v>0.8246805111821086</v>
+        <v>0</v>
       </c>
       <c r="U7">
-        <v>9.17</v>
+        <v>56.6</v>
       </c>
       <c r="V7">
-        <v>0.04692937563971341</v>
+        <v>0.881619937694704</v>
       </c>
       <c r="W7">
-        <v>0.2047092743873138</v>
+        <v>0.08146666666666667</v>
       </c>
       <c r="X7">
-        <v>0.1059722643170933</v>
+        <v>0.08479692846796255</v>
       </c>
       <c r="Y7">
-        <v>0.09873701007022054</v>
+        <v>-0.003330261801295878</v>
       </c>
       <c r="Z7">
-        <v>0.2330102086793084</v>
+        <v>0</v>
       </c>
       <c r="AA7">
-        <v>0.187986136630185</v>
+        <v>0.2247259666845185</v>
       </c>
       <c r="AB7">
-        <v>0.102443745850982</v>
+        <v>0.08479692846796255</v>
       </c>
       <c r="AC7">
-        <v>0.085542390779203</v>
+        <v>0.1399290382165559</v>
       </c>
       <c r="AD7">
-        <v>16.8</v>
+        <v>0</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>16.8</v>
+        <v>0</v>
       </c>
       <c r="AG7">
-        <v>7.630000000000001</v>
+        <v>-56.6</v>
       </c>
       <c r="AH7">
-        <v>0.07917059377945335</v>
+        <v>0</v>
       </c>
       <c r="AI7">
-        <v>0.06749698674166332</v>
+        <v>0</v>
       </c>
       <c r="AJ7">
-        <v>0.0375806531054524</v>
+        <v>-7.44736842105263</v>
       </c>
       <c r="AK7">
-        <v>0.03182747257331164</v>
+        <v>-3.215909090909091</v>
       </c>
       <c r="AL7">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AM7">
-        <v>1.25</v>
-      </c>
-      <c r="AN7">
-        <v>0.3492723492723493</v>
-      </c>
-      <c r="AO7">
-        <v>38.4</v>
-      </c>
-      <c r="AP7">
-        <v>0.1586278586278586</v>
+        <v>-2.87</v>
       </c>
       <c r="AQ7">
-        <v>38.4</v>
+        <v>-1.738675958188153</v>
       </c>
     </row>
     <row r="8">
@@ -1392,7 +1359,7 @@
         </is>
       </c>
       <c r="D8">
-        <v>1.16</v>
+        <v>1.374</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1401,34 +1368,34 @@
         <v>0</v>
       </c>
       <c r="I8">
-        <v>0.9833333333333334</v>
+        <v>0.9753694581280788</v>
       </c>
       <c r="J8">
-        <v>0.9833333333333334</v>
+        <v>0.9753694581280788</v>
       </c>
       <c r="K8">
-        <v>-79.5</v>
+        <v>-73.7</v>
       </c>
       <c r="L8">
-        <v>-1.472222222222222</v>
+        <v>-1.815270935960591</v>
       </c>
       <c r="M8">
-        <v>6.47</v>
+        <v>4.52</v>
       </c>
       <c r="N8">
-        <v>0.05587219343696027</v>
+        <v>0.0488120950323974</v>
       </c>
       <c r="O8">
-        <v>-0.08138364779874213</v>
+        <v>-0.06132971506105834</v>
       </c>
       <c r="P8">
-        <v>6.47</v>
+        <v>4.52</v>
       </c>
       <c r="Q8">
-        <v>0.05587219343696027</v>
+        <v>0.0488120950323974</v>
       </c>
       <c r="R8">
-        <v>-0.08138364779874213</v>
+        <v>-0.06132971506105834</v>
       </c>
       <c r="S8">
         <v>0</v>
@@ -1437,67 +1404,67 @@
         <v>0</v>
       </c>
       <c r="U8">
-        <v>0.311</v>
+        <v>0.306</v>
       </c>
       <c r="V8">
-        <v>0.00268566493955095</v>
+        <v>0.003304535637149028</v>
       </c>
       <c r="W8">
-        <v>-0.2207107162687396</v>
+        <v>-0.344392523364486</v>
       </c>
       <c r="X8">
-        <v>0.2977211229349253</v>
+        <v>0.2550426874146919</v>
       </c>
       <c r="Y8">
-        <v>-0.5184318392036649</v>
+        <v>-0.5994352107791779</v>
       </c>
       <c r="Z8">
-        <v>0.05548551365714269</v>
+        <v>0.05759772105962783</v>
       </c>
       <c r="AA8">
-        <v>0.05456075509619032</v>
+        <v>0.05617905797934143</v>
       </c>
       <c r="AB8">
-        <v>0.1064870035202336</v>
+        <v>0.0930108546268012</v>
       </c>
       <c r="AC8">
-        <v>-0.05192624842404327</v>
+        <v>-0.03683179664745977</v>
       </c>
       <c r="AD8">
-        <v>491.2</v>
+        <v>469.5</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>491.2</v>
+        <v>469.5</v>
       </c>
       <c r="AG8">
-        <v>490.889</v>
+        <v>469.194</v>
       </c>
       <c r="AH8">
-        <v>0.8092257001647446</v>
+        <v>0.8352606297811777</v>
       </c>
       <c r="AI8">
-        <v>0.6965399886557004</v>
+        <v>0.7881483968440489</v>
       </c>
       <c r="AJ8">
-        <v>0.809127905730943</v>
+        <v>0.835170898941605</v>
       </c>
       <c r="AK8">
-        <v>0.6964061008187105</v>
+        <v>0.7880395166897887</v>
       </c>
       <c r="AL8">
-        <v>27</v>
+        <v>35.3</v>
       </c>
       <c r="AM8">
-        <v>26.971</v>
+        <v>35.242</v>
       </c>
       <c r="AO8">
-        <v>1.966666666666667</v>
+        <v>1.121813031161473</v>
       </c>
       <c r="AQ8">
-        <v>1.968781283600905</v>
+        <v>1.123659270188979</v>
       </c>
     </row>
     <row r="9">
@@ -1516,6 +1483,9 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="D9">
+        <v>-0.14</v>
+      </c>
       <c r="G9">
         <v>0</v>
       </c>
@@ -1523,16 +1493,16 @@
         <v>0</v>
       </c>
       <c r="I9">
-        <v>0.9361702127659575</v>
+        <v>0.9333333333333333</v>
       </c>
       <c r="J9">
-        <v>0.9361702127659575</v>
+        <v>0.9333333333333333</v>
       </c>
       <c r="K9">
-        <v>27.3</v>
+        <v>-31.2</v>
       </c>
       <c r="L9">
-        <v>1.936170212765957</v>
+        <v>-2.311111111111111</v>
       </c>
       <c r="M9">
         <v>-0</v>
@@ -1541,7 +1511,7 @@
         <v>-0</v>
       </c>
       <c r="O9">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P9">
         <v>-0</v>
@@ -1550,73 +1520,73 @@
         <v>-0</v>
       </c>
       <c r="R9">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S9">
         <v>0</v>
       </c>
       <c r="U9">
-        <v>1.79</v>
+        <v>4.2</v>
       </c>
       <c r="V9">
-        <v>0.01271306818181818</v>
+        <v>0.03626943005181348</v>
       </c>
       <c r="W9">
-        <v>0.1153358681875792</v>
+        <v>-0.1060863651819109</v>
       </c>
       <c r="X9">
-        <v>0.1193404901613316</v>
+        <v>0.09604750706836471</v>
       </c>
       <c r="Y9">
-        <v>-0.00400462197375237</v>
+        <v>-0.2021338722502756</v>
       </c>
       <c r="Z9">
-        <v>0.04623360100730228</v>
+        <v>0.03910663074650213</v>
       </c>
       <c r="AA9">
-        <v>0.04328252009194256</v>
+        <v>0.03649952203006866</v>
       </c>
       <c r="AB9">
-        <v>0.1050529089817313</v>
+        <v>0.08620015527012151</v>
       </c>
       <c r="AC9">
-        <v>-0.06177038888978877</v>
+        <v>-0.04970063324005285</v>
       </c>
       <c r="AD9">
-        <v>52.9</v>
+        <v>38.8</v>
       </c>
       <c r="AE9">
         <v>0</v>
       </c>
       <c r="AF9">
-        <v>52.9</v>
+        <v>38.8</v>
       </c>
       <c r="AG9">
-        <v>51.11</v>
+        <v>34.59999999999999</v>
       </c>
       <c r="AH9">
-        <v>0.2731027361899845</v>
+        <v>0.2509702457956016</v>
       </c>
       <c r="AI9">
-        <v>0.1524495677233429</v>
+        <v>0.13997113997114</v>
       </c>
       <c r="AJ9">
-        <v>0.2663227554582877</v>
+        <v>0.2300531914893617</v>
       </c>
       <c r="AK9">
-        <v>0.1480548072187943</v>
+        <v>0.1267399267399267</v>
       </c>
       <c r="AL9">
-        <v>3.89</v>
+        <v>2.82</v>
       </c>
       <c r="AM9">
-        <v>3.842</v>
+        <v>2.67</v>
       </c>
       <c r="AO9">
-        <v>3.39331619537275</v>
+        <v>4.468085106382979</v>
       </c>
       <c r="AQ9">
-        <v>3.435710567412805</v>
+        <v>4.719101123595506</v>
       </c>
     </row>
     <row r="10">
@@ -1627,7 +1597,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>PSG Konsult Limited (JSE:KST)</t>
+          <t>Purple Group Limited (JSE:PPE)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1636,13 +1606,10 @@
         </is>
       </c>
       <c r="D10">
-        <v>0.106</v>
-      </c>
-      <c r="E10">
-        <v>0.126</v>
+        <v>0.342</v>
       </c>
       <c r="G10">
-        <v>0</v>
+        <v>0.002206896551724138</v>
       </c>
       <c r="H10">
         <v>0</v>
@@ -1654,91 +1621,91 @@
         <v>0</v>
       </c>
       <c r="K10">
-        <v>54.3</v>
+        <v>-1.32</v>
       </c>
       <c r="L10">
-        <v>0.1486042692939245</v>
+        <v>-0.09103448275862069</v>
       </c>
       <c r="M10">
-        <v>39</v>
+        <v>-0</v>
       </c>
       <c r="N10">
-        <v>0.04240513210829618</v>
+        <v>-0</v>
       </c>
       <c r="O10">
-        <v>0.7182320441988951</v>
+        <v>0</v>
       </c>
       <c r="P10">
-        <v>24.7</v>
+        <v>-0</v>
       </c>
       <c r="Q10">
-        <v>0.02685658366858758</v>
+        <v>-0</v>
       </c>
       <c r="R10">
-        <v>0.4548802946593002</v>
+        <v>0</v>
       </c>
       <c r="S10">
-        <v>14.3</v>
-      </c>
-      <c r="T10">
-        <v>0.3666666666666667</v>
+        <v>0</v>
       </c>
       <c r="U10">
-        <v>114.8</v>
+        <v>9.91</v>
       </c>
       <c r="V10">
-        <v>0.1248233119495488</v>
+        <v>0.1825046040515654</v>
       </c>
       <c r="W10">
-        <v>0.2102206736353077</v>
+        <v>-0.04697508896797153</v>
       </c>
       <c r="X10">
-        <v>0.1027728521473979</v>
+        <v>0.08489648682897247</v>
       </c>
       <c r="Y10">
-        <v>0.1074478214879099</v>
+        <v>-0.131871575796944</v>
       </c>
       <c r="Z10">
-        <v>2.244471744471744</v>
+        <v>2.196969696969698</v>
       </c>
       <c r="AA10">
         <v>0</v>
       </c>
       <c r="AB10">
-        <v>0.1020959026401986</v>
+        <v>0.084826000075532</v>
       </c>
       <c r="AC10">
-        <v>-0.1020959026401986</v>
+        <v>-0.084826000075532</v>
       </c>
       <c r="AD10">
-        <v>15.3</v>
+        <v>0.161</v>
       </c>
       <c r="AE10">
         <v>0</v>
       </c>
       <c r="AF10">
-        <v>15.3</v>
+        <v>0.161</v>
       </c>
       <c r="AG10">
-        <v>-99.5</v>
+        <v>-9.749000000000001</v>
       </c>
       <c r="AH10">
-        <v>0.01636363636363636</v>
+        <v>0.002956243917665853</v>
       </c>
       <c r="AI10">
-        <v>0.05385427666314678</v>
+        <v>0.004464657108787887</v>
       </c>
       <c r="AJ10">
-        <v>-0.1213118751524018</v>
+        <v>-0.2188278602051582</v>
       </c>
       <c r="AK10">
-        <v>-0.5877141169521559</v>
+        <v>-0.3727964513785325</v>
       </c>
       <c r="AL10">
         <v>0</v>
       </c>
       <c r="AM10">
-        <v>0</v>
+        <v>-0.579</v>
+      </c>
+      <c r="AQ10">
+        <v>-0</v>
       </c>
     </row>
     <row r="11">
@@ -1749,7 +1716,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Purple Group Limited (JSE:PPE)</t>
+          <t>PSG Financial Services Limited (JSE:KST)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1758,10 +1725,13 @@
         </is>
       </c>
       <c r="D11">
-        <v>0.312</v>
+        <v>0.0959</v>
+      </c>
+      <c r="E11">
+        <v>0.11</v>
       </c>
       <c r="G11">
-        <v>0.001949685534591195</v>
+        <v>0</v>
       </c>
       <c r="H11">
         <v>0</v>
@@ -1773,91 +1743,91 @@
         <v>0</v>
       </c>
       <c r="K11">
-        <v>2.58</v>
+        <v>54.2</v>
       </c>
       <c r="L11">
-        <v>0.1622641509433962</v>
+        <v>0.1491469455145845</v>
       </c>
       <c r="M11">
-        <v>-0</v>
+        <v>43.6</v>
       </c>
       <c r="N11">
-        <v>-0</v>
+        <v>0.04078959678173823</v>
       </c>
       <c r="O11">
-        <v>-0</v>
+        <v>0.8044280442804428</v>
       </c>
       <c r="P11">
-        <v>-0</v>
+        <v>24.5</v>
       </c>
       <c r="Q11">
-        <v>-0</v>
+        <v>0.022920759659463</v>
       </c>
       <c r="R11">
-        <v>-0</v>
+        <v>0.4520295202952029</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>19.1</v>
+      </c>
+      <c r="T11">
+        <v>0.4380733944954129</v>
       </c>
       <c r="U11">
-        <v>5.55</v>
+        <v>78.2</v>
       </c>
       <c r="V11">
-        <v>0.04356357927786499</v>
+        <v>0.07315932266816352</v>
       </c>
       <c r="W11">
-        <v>0.09626865671641791</v>
+        <v>0.2235051546391753</v>
       </c>
       <c r="X11">
-        <v>0.1024217660847348</v>
+        <v>0.08516760630669679</v>
       </c>
       <c r="Y11">
-        <v>-0.006153109368316867</v>
+        <v>0.1383375483324785</v>
       </c>
       <c r="Z11">
-        <v>3.111545988258317</v>
+        <v>2.541258741258741</v>
       </c>
       <c r="AA11">
         <v>0</v>
       </c>
       <c r="AB11">
-        <v>0.1021051063565227</v>
+        <v>0.08485797802134105</v>
       </c>
       <c r="AC11">
-        <v>-0.1021051063565227</v>
+        <v>-0.08485797802134105</v>
       </c>
       <c r="AD11">
-        <v>1.15</v>
+        <v>11.8</v>
       </c>
       <c r="AE11">
         <v>0</v>
       </c>
       <c r="AF11">
-        <v>1.15</v>
+        <v>11.8</v>
       </c>
       <c r="AG11">
-        <v>-4.4</v>
+        <v>-66.40000000000001</v>
       </c>
       <c r="AH11">
-        <v>0.00894593543368339</v>
+        <v>0.01091884889423522</v>
       </c>
       <c r="AI11">
-        <v>0.03427719821162444</v>
+        <v>0.04389880952380953</v>
       </c>
       <c r="AJ11">
-        <v>-0.03577235772357724</v>
+        <v>-0.06623441396508728</v>
       </c>
       <c r="AK11">
-        <v>-0.1571428571428572</v>
+        <v>-0.348373557187828</v>
       </c>
       <c r="AL11">
         <v>0</v>
       </c>
       <c r="AM11">
-        <v>-0.427</v>
-      </c>
-      <c r="AQ11">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1868,7 +1838,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Zeder Investments Ltd. (JSE:ZED)</t>
+          <t>African Equity Empowerment Investments Limited (JSE:AEE)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1876,8 +1846,26 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="D12">
+        <v>0.009399999999999999</v>
+      </c>
+      <c r="G12">
+        <v>0.02275773195876289</v>
+      </c>
+      <c r="H12">
+        <v>0.02275773195876289</v>
+      </c>
+      <c r="I12">
+        <v>-0.0007216494845360826</v>
+      </c>
+      <c r="J12">
+        <v>-0.0007216494845360826</v>
+      </c>
       <c r="K12">
-        <v>6.51</v>
+        <v>-91.5</v>
+      </c>
+      <c r="L12">
+        <v>-2.358247422680412</v>
       </c>
       <c r="M12">
         <v>-0</v>
@@ -1886,7 +1874,7 @@
         <v>-0</v>
       </c>
       <c r="O12">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P12">
         <v>-0</v>
@@ -1895,70 +1883,79 @@
         <v>-0</v>
       </c>
       <c r="R12">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S12">
         <v>0</v>
       </c>
       <c r="U12">
-        <v>25.9</v>
+        <v>12.5</v>
       </c>
       <c r="V12">
-        <v>0.1665594855305466</v>
+        <v>0.4280821917808219</v>
       </c>
       <c r="W12">
-        <v>0.01379237288135593</v>
+        <v>-0.6067639257294429</v>
       </c>
       <c r="X12">
-        <v>0.1020052760592112</v>
+        <v>0.09418030187542689</v>
       </c>
       <c r="Y12">
-        <v>-0.08821290317785524</v>
+        <v>-0.7009442276048699</v>
       </c>
       <c r="Z12">
-        <v>0</v>
+        <v>0.511468494595307</v>
       </c>
       <c r="AA12">
-        <v>-0.004280510018214936</v>
+        <v>-0.0003691009754811494</v>
       </c>
       <c r="AB12">
-        <v>0.1020052760592112</v>
+        <v>0.08737037270385103</v>
       </c>
       <c r="AC12">
-        <v>-0.1062857860774261</v>
+        <v>-0.08773947367933219</v>
       </c>
       <c r="AD12">
-        <v>0</v>
+        <v>8.16</v>
       </c>
       <c r="AE12">
         <v>0</v>
       </c>
       <c r="AF12">
-        <v>0</v>
+        <v>8.16</v>
       </c>
       <c r="AG12">
-        <v>-25.9</v>
+        <v>-4.34</v>
       </c>
       <c r="AH12">
-        <v>0</v>
+        <v>0.2184154175588865</v>
       </c>
       <c r="AI12">
-        <v>0</v>
+        <v>0.1132389675270608</v>
       </c>
       <c r="AJ12">
-        <v>-0.1998456790123457</v>
+        <v>-0.1745776347546259</v>
       </c>
       <c r="AK12">
-        <v>-0.1192998618148319</v>
+        <v>-0.07286769644056414</v>
       </c>
       <c r="AL12">
-        <v>0</v>
+        <v>0.308</v>
       </c>
       <c r="AM12">
-        <v>-2.29</v>
+        <v>-0.4</v>
+      </c>
+      <c r="AN12">
+        <v>9.241223103057758</v>
+      </c>
+      <c r="AO12">
+        <v>-0.09090909090909091</v>
+      </c>
+      <c r="AP12">
+        <v>-4.915062287655719</v>
       </c>
       <c r="AQ12">
-        <v>0.8209606986899562</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="13">
@@ -1969,7 +1966,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Mahube Infrastructure Limited (JSE:MHB)</t>
+          <t>Zeder Investments Ltd. (JSE:ZED)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1978,103 +1975,94 @@
         </is>
       </c>
       <c r="E13">
-        <v>0.0537</v>
+        <v>-0.336</v>
       </c>
       <c r="K13">
-        <v>2.83</v>
+        <v>4.02</v>
       </c>
       <c r="M13">
-        <v>1.94</v>
+        <v>0.846</v>
       </c>
       <c r="N13">
-        <v>0.1026455026455027</v>
+        <v>0.005727826675693975</v>
       </c>
       <c r="O13">
-        <v>0.6855123674911661</v>
+        <v>0.2104477611940299</v>
       </c>
       <c r="P13">
-        <v>1.94</v>
+        <v>-0</v>
       </c>
       <c r="Q13">
-        <v>0.1026455026455027</v>
+        <v>-0</v>
       </c>
       <c r="R13">
-        <v>0.6855123674911661</v>
+        <v>-0</v>
       </c>
       <c r="S13">
-        <v>0</v>
+        <v>0.846</v>
       </c>
       <c r="T13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U13">
-        <v>1.47</v>
+        <v>23.2</v>
       </c>
       <c r="V13">
-        <v>0.07777777777777778</v>
+        <v>0.1570751523358158</v>
       </c>
       <c r="W13">
-        <v>0.06819277108433736</v>
+        <v>0.01654320987654321</v>
       </c>
       <c r="X13">
-        <v>0.1020321299410501</v>
+        <v>0.08479692846796255</v>
       </c>
       <c r="Y13">
-        <v>-0.03383935885671271</v>
+        <v>-0.06825371859141935</v>
       </c>
       <c r="Z13">
         <v>0</v>
       </c>
       <c r="AA13">
-        <v>-0.01931177598936593</v>
+        <v>-0.005689265246331371</v>
       </c>
       <c r="AB13">
-        <v>0.1020117671068376</v>
+        <v>0.08479692846796255</v>
       </c>
       <c r="AC13">
-        <v>-0.1213235430962036</v>
+        <v>-0.09048619371429392</v>
       </c>
       <c r="AD13">
-        <v>0.011</v>
+        <v>0</v>
       </c>
       <c r="AE13">
         <v>0</v>
       </c>
       <c r="AF13">
-        <v>0.011</v>
+        <v>0</v>
       </c>
       <c r="AG13">
-        <v>-1.459</v>
+        <v>-23.2</v>
       </c>
       <c r="AH13">
-        <v>0.0005816720427264555</v>
+        <v>0</v>
       </c>
       <c r="AI13">
-        <v>0.0003037750959653144</v>
+        <v>0</v>
       </c>
       <c r="AJ13">
-        <v>-0.08365346023737172</v>
+        <v>-0.1863453815261044</v>
       </c>
       <c r="AK13">
-        <v>-0.04199648829912783</v>
+        <v>-0.1219768664563617</v>
       </c>
       <c r="AL13">
-        <v>0.004</v>
+        <v>0</v>
       </c>
       <c r="AM13">
-        <v>-2.086</v>
-      </c>
-      <c r="AN13">
-        <v>-0.01381909547738693</v>
-      </c>
-      <c r="AO13">
-        <v>-200.75</v>
-      </c>
-      <c r="AP13">
-        <v>1.832914572864322</v>
+        <v>-2.38</v>
       </c>
       <c r="AQ13">
-        <v>0.3849472674976031</v>
+        <v>0.6008403361344538</v>
       </c>
     </row>
     <row r="14">
@@ -2094,40 +2082,40 @@
         </is>
       </c>
       <c r="G14">
-        <v>13.37579617834395</v>
+        <v>-1.637096774193548</v>
       </c>
       <c r="H14">
-        <v>13.37579617834395</v>
+        <v>-1.637096774193548</v>
       </c>
       <c r="I14">
-        <v>-3.821656050955414</v>
+        <v>-0.3080645161290322</v>
       </c>
       <c r="J14">
-        <v>-3.821656050955414</v>
+        <v>-0.3080645161290322</v>
       </c>
       <c r="K14">
-        <v>-0.784</v>
+        <v>-1.01</v>
       </c>
       <c r="L14">
-        <v>-2.496815286624204</v>
+        <v>-0.8145161290322581</v>
       </c>
       <c r="M14">
-        <v>0.229</v>
+        <v>1.0352</v>
       </c>
       <c r="N14">
-        <v>0.02729439809296782</v>
+        <v>0.0985904761904762</v>
       </c>
       <c r="O14">
-        <v>-0.2920918367346939</v>
+        <v>-1.024950495049505</v>
       </c>
       <c r="P14">
-        <v>0.229</v>
+        <v>1.0352</v>
       </c>
       <c r="Q14">
-        <v>0.02729439809296782</v>
+        <v>0.0985904761904762</v>
       </c>
       <c r="R14">
-        <v>-0.2920918367346939</v>
+        <v>-1.024950495049505</v>
       </c>
       <c r="S14">
         <v>0</v>
@@ -2136,73 +2124,73 @@
         <v>0</v>
       </c>
       <c r="U14">
-        <v>2.48</v>
+        <v>5.88</v>
       </c>
       <c r="V14">
-        <v>0.2955899880810489</v>
+        <v>0.5599999999999999</v>
       </c>
       <c r="W14">
-        <v>-0.01226917057902973</v>
+        <v>-0.01894934333958724</v>
       </c>
       <c r="X14">
-        <v>0.1192733492156979</v>
+        <v>0.1026411083176196</v>
       </c>
       <c r="Y14">
-        <v>-0.1315425197947276</v>
+        <v>-0.1215904516572068</v>
       </c>
       <c r="Z14">
-        <v>0.004978516275308779</v>
+        <v>0.02297998517420311</v>
       </c>
       <c r="AA14">
-        <v>-0.0190261768483138</v>
+        <v>-0.007079318013343217</v>
       </c>
       <c r="AB14">
-        <v>0.105799771629851</v>
+        <v>0.08888557554905976</v>
       </c>
       <c r="AC14">
-        <v>-0.1248259484781648</v>
+        <v>-0.09596489356240298</v>
       </c>
       <c r="AD14">
-        <v>3.14</v>
+        <v>5.58</v>
       </c>
       <c r="AE14">
         <v>0</v>
       </c>
       <c r="AF14">
-        <v>3.14</v>
+        <v>5.58</v>
       </c>
       <c r="AG14">
-        <v>0.6600000000000001</v>
+        <v>-0.2999999999999998</v>
       </c>
       <c r="AH14">
-        <v>0.2723330442324371</v>
+        <v>0.3470149253731344</v>
       </c>
       <c r="AI14">
-        <v>0.0556343019135365</v>
+        <v>0.1059225512528474</v>
       </c>
       <c r="AJ14">
-        <v>0.07292817679558013</v>
+        <v>-0.02941176470588234</v>
       </c>
       <c r="AK14">
-        <v>0.01223128243143069</v>
+        <v>-0.006410256410256406</v>
       </c>
       <c r="AL14">
-        <v>0.068</v>
+        <v>0.889</v>
       </c>
       <c r="AM14">
-        <v>0.068</v>
+        <v>0.889</v>
       </c>
       <c r="AN14">
-        <v>-2.638655462184874</v>
+        <v>-14.76190476190476</v>
       </c>
       <c r="AO14">
-        <v>-17.64705882352941</v>
+        <v>-0.4296962879640045</v>
       </c>
       <c r="AP14">
-        <v>-0.5546218487394959</v>
+        <v>0.7936507936507932</v>
       </c>
       <c r="AQ14">
-        <v>-17.64705882352941</v>
+        <v>-0.4296962879640045</v>
       </c>
     </row>
     <row r="15">
@@ -2213,7 +2201,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>African Equity Empowerment Investments Limited (JSE:AEE)</t>
+          <t>Mahube Infrastructure Limited (JSE:MHB)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2221,44 +2209,26 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="D15">
-        <v>0.26</v>
-      </c>
-      <c r="G15">
-        <v>-0.1730192188468692</v>
-      </c>
-      <c r="H15">
-        <v>-0.1735895846249225</v>
-      </c>
-      <c r="I15">
-        <v>-0.2145071295722256</v>
-      </c>
-      <c r="J15">
-        <v>-0.2145071295722256</v>
-      </c>
       <c r="K15">
-        <v>-9.18</v>
-      </c>
-      <c r="L15">
-        <v>-0.0569125852448853</v>
+        <v>-1.02</v>
       </c>
       <c r="M15">
-        <v>16.8</v>
+        <v>1.31</v>
       </c>
       <c r="N15">
-        <v>0.6774193548387097</v>
+        <v>0.1082644628099174</v>
       </c>
       <c r="O15">
-        <v>-1.830065359477124</v>
+        <v>-1.284313725490196</v>
       </c>
       <c r="P15">
-        <v>16.8</v>
+        <v>1.31</v>
       </c>
       <c r="Q15">
-        <v>0.6774193548387097</v>
+        <v>0.1082644628099174</v>
       </c>
       <c r="R15">
-        <v>-1.830065359477124</v>
+        <v>-1.284313725490196</v>
       </c>
       <c r="S15">
         <v>0</v>
@@ -2267,64 +2237,70 @@
         <v>0</v>
       </c>
       <c r="U15">
-        <v>161.7</v>
+        <v>0.362</v>
       </c>
       <c r="V15">
-        <v>6.52016129032258</v>
+        <v>0.02991735537190083</v>
       </c>
       <c r="W15">
-        <v>-0.04870026525198939</v>
+        <v>-0.0281767955801105</v>
       </c>
       <c r="X15">
-        <v>0.130284539896026</v>
+        <v>0.08479692846796255</v>
       </c>
       <c r="Y15">
-        <v>-0.1789848051480153</v>
+        <v>-0.112973724048073</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+      <c r="AA15">
+        <v>-0.02190495380098442</v>
       </c>
       <c r="AB15">
-        <v>0.1072999266621416</v>
+        <v>0.08479692846796255</v>
+      </c>
+      <c r="AC15">
+        <v>-0.106701882268947</v>
       </c>
       <c r="AD15">
-        <v>15.2</v>
+        <v>0</v>
       </c>
       <c r="AE15">
         <v>0</v>
       </c>
       <c r="AF15">
-        <v>15.2</v>
+        <v>0</v>
       </c>
       <c r="AG15">
-        <v>-146.5</v>
+        <v>-0.362</v>
       </c>
       <c r="AH15">
-        <v>0.38</v>
+        <v>0</v>
       </c>
       <c r="AI15">
-        <v>0.0391147709727226</v>
+        <v>0</v>
       </c>
       <c r="AJ15">
-        <v>1.203779786359901</v>
+        <v>-0.03084000681547112</v>
       </c>
       <c r="AK15">
-        <v>-0.6456588805641252</v>
+        <v>-0.01209165608925112</v>
       </c>
       <c r="AL15">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AM15">
-        <v>-9.68</v>
+        <v>-1.64</v>
       </c>
       <c r="AN15">
-        <v>-0.5428571428571428</v>
-      </c>
-      <c r="AO15">
-        <v>-22.76315789473684</v>
+        <v>-0</v>
       </c>
       <c r="AP15">
-        <v>5.232142857142857</v>
+        <v>0.4677002583979328</v>
       </c>
       <c r="AQ15">
-        <v>3.574380165289257</v>
+        <v>0.4640243902439025</v>
       </c>
     </row>
   </sheetData>
